--- a/db_initializer/facilities/tl_health_facilities_edited.xlsx
+++ b/db_initializer/facilities/tl_health_facilities_edited.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c2399de6ce21ea9a/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ericksoncruz/Documents/RIMES/superset/db_initializer/facilities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{9CB7B245-50CE-40CE-A6F0-C847AD82A1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBBBC1F8-7C95-47A4-A2DD-B79FD8D1F0EB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0BE0E1-0BBF-6847-B349-022E07910FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="7" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TL Health Facilities" sheetId="22" r:id="rId1"/>
@@ -23330,7 +23330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="304">
+  <cellXfs count="301">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -24045,15 +24045,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -24195,13 +24186,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -24225,19 +24222,13 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -24558,7 +24549,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A42BD1B-2387-48F2-8274-5DB52C62818F}">
   <dimension ref="A1:N71"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="5" width="8.796875" style="8"/>
@@ -24566,94 +24557,94 @@
     <col min="7" max="16384" width="8.796875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="24.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="291" t="s">
+    <row r="1" spans="1:14" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="290" t="s">
         <v>1358</v>
       </c>
-      <c r="B1" s="292"/>
-      <c r="C1" s="292"/>
-      <c r="D1" s="292"/>
-      <c r="E1" s="292"/>
-      <c r="F1" s="292"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="286" t="s">
+      <c r="B1" s="291"/>
+      <c r="C1" s="291"/>
+      <c r="D1" s="291"/>
+      <c r="E1" s="291"/>
+      <c r="F1" s="291"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A2" s="283" t="s">
         <v>1359</v>
       </c>
-      <c r="B2" s="287" t="s">
+      <c r="B2" s="284" t="s">
         <v>1360</v>
       </c>
-      <c r="C2" s="287"/>
-      <c r="D2" s="287"/>
-      <c r="E2" s="287"/>
+      <c r="C2" s="284"/>
+      <c r="D2" s="284"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="286"/>
-      <c r="B3" s="287" t="s">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A3" s="283"/>
+      <c r="B3" s="284" t="s">
         <v>721</v>
       </c>
-      <c r="C3" s="287"/>
-      <c r="D3" s="287"/>
-      <c r="E3" s="287"/>
+      <c r="C3" s="284"/>
+      <c r="D3" s="284"/>
+      <c r="E3" s="284"/>
       <c r="F3" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="286"/>
-      <c r="B4" s="287" t="s">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A4" s="283"/>
+      <c r="B4" s="284" t="s">
         <v>723</v>
       </c>
-      <c r="C4" s="287"/>
-      <c r="D4" s="287"/>
-      <c r="E4" s="287"/>
+      <c r="C4" s="284"/>
+      <c r="D4" s="284"/>
+      <c r="E4" s="284"/>
       <c r="F4" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="286"/>
-      <c r="B5" s="287" t="s">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A5" s="283"/>
+      <c r="B5" s="284" t="s">
         <v>1356</v>
       </c>
-      <c r="C5" s="287"/>
-      <c r="D5" s="287"/>
-      <c r="E5" s="287"/>
+      <c r="C5" s="284"/>
+      <c r="D5" s="284"/>
+      <c r="E5" s="284"/>
       <c r="F5" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="286"/>
-      <c r="B6" s="287" t="s">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A6" s="283"/>
+      <c r="B6" s="284" t="s">
         <v>1357</v>
       </c>
-      <c r="C6" s="287"/>
-      <c r="D6" s="287"/>
-      <c r="E6" s="287"/>
+      <c r="C6" s="284"/>
+      <c r="D6" s="284"/>
+      <c r="E6" s="284"/>
       <c r="F6" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="286" t="s">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A7" s="283" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="287" t="s">
+      <c r="B7" s="284" t="s">
         <v>730</v>
       </c>
-      <c r="C7" s="287"/>
-      <c r="D7" s="287"/>
-      <c r="E7" s="287"/>
+      <c r="C7" s="284"/>
+      <c r="D7" s="284"/>
+      <c r="E7" s="284"/>
       <c r="F7" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="286"/>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A8" s="283"/>
       <c r="B8" s="2" t="s">
         <v>1360</v>
       </c>
@@ -24663,839 +24654,870 @@
       <c r="F8" s="6">
         <v>1</v>
       </c>
-      <c r="K8" s="293" t="s">
+      <c r="K8" s="292" t="s">
         <v>741</v>
       </c>
-      <c r="L8" s="293"/>
-      <c r="M8" s="293"/>
-      <c r="N8" s="293"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="286"/>
-      <c r="B9" s="287" t="s">
+      <c r="L8" s="292"/>
+      <c r="M8" s="292"/>
+      <c r="N8" s="292"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A9" s="283"/>
+      <c r="B9" s="284" t="s">
         <v>721</v>
       </c>
-      <c r="C9" s="287"/>
-      <c r="D9" s="287"/>
-      <c r="E9" s="287"/>
+      <c r="C9" s="284"/>
+      <c r="D9" s="284"/>
+      <c r="E9" s="284"/>
       <c r="F9" s="6">
         <v>3</v>
       </c>
-      <c r="K9" s="294" t="s">
+      <c r="K9" s="293" t="s">
         <v>732</v>
       </c>
-      <c r="L9" s="294"/>
-      <c r="M9" s="294"/>
-      <c r="N9" s="294"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="286"/>
-      <c r="B10" s="287" t="s">
+      <c r="L9" s="293"/>
+      <c r="M9" s="293"/>
+      <c r="N9" s="293"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A10" s="283"/>
+      <c r="B10" s="284" t="s">
         <v>723</v>
       </c>
-      <c r="C10" s="287"/>
-      <c r="D10" s="287"/>
-      <c r="E10" s="287"/>
+      <c r="C10" s="284"/>
+      <c r="D10" s="284"/>
+      <c r="E10" s="284"/>
       <c r="F10" s="6">
         <v>22</v>
       </c>
-      <c r="K10" s="295" t="s">
+      <c r="K10" s="294" t="s">
         <v>730</v>
       </c>
-      <c r="L10" s="295"/>
-      <c r="M10" s="295"/>
-      <c r="N10" s="295"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="286"/>
-      <c r="B11" s="287" t="s">
+      <c r="L10" s="294"/>
+      <c r="M10" s="294"/>
+      <c r="N10" s="294"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A11" s="283"/>
+      <c r="B11" s="284" t="s">
         <v>1356</v>
       </c>
-      <c r="C11" s="287"/>
-      <c r="D11" s="287"/>
-      <c r="E11" s="287"/>
+      <c r="C11" s="284"/>
+      <c r="D11" s="284"/>
+      <c r="E11" s="284"/>
       <c r="F11" s="6">
         <v>3</v>
       </c>
-      <c r="K11" s="296" t="s">
+      <c r="K11" s="295" t="s">
         <v>1360</v>
       </c>
-      <c r="L11" s="296"/>
-      <c r="M11" s="296"/>
-      <c r="N11" s="296"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="286" t="s">
+      <c r="L11" s="295"/>
+      <c r="M11" s="295"/>
+      <c r="N11" s="295"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A12" s="283" t="s">
         <v>1361</v>
       </c>
-      <c r="B12" s="287" t="s">
+      <c r="B12" s="284" t="s">
         <v>721</v>
       </c>
-      <c r="C12" s="287"/>
-      <c r="D12" s="287"/>
-      <c r="E12" s="287"/>
+      <c r="C12" s="284"/>
+      <c r="D12" s="284"/>
+      <c r="E12" s="284"/>
       <c r="F12" s="6">
         <v>1</v>
       </c>
-      <c r="K12" s="297" t="s">
+      <c r="K12" s="296" t="s">
         <v>721</v>
       </c>
-      <c r="L12" s="297"/>
-      <c r="M12" s="297"/>
-      <c r="N12" s="297"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="286"/>
-      <c r="B13" s="287" t="s">
+      <c r="L12" s="296"/>
+      <c r="M12" s="296"/>
+      <c r="N12" s="296"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A13" s="283"/>
+      <c r="B13" s="284" t="s">
         <v>723</v>
       </c>
-      <c r="C13" s="287"/>
-      <c r="D13" s="287"/>
-      <c r="E13" s="287"/>
+      <c r="C13" s="284"/>
+      <c r="D13" s="284"/>
+      <c r="E13" s="284"/>
       <c r="F13" s="6">
         <v>6</v>
       </c>
-      <c r="K13" s="288" t="s">
+      <c r="K13" s="298" t="s">
         <v>723</v>
       </c>
-      <c r="L13" s="288"/>
-      <c r="M13" s="288"/>
-      <c r="N13" s="288"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="286" t="s">
+      <c r="L13" s="298"/>
+      <c r="M13" s="298"/>
+      <c r="N13" s="298"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A14" s="283" t="s">
         <v>1362</v>
       </c>
-      <c r="B14" s="287" t="s">
+      <c r="B14" s="284" t="s">
         <v>732</v>
       </c>
-      <c r="C14" s="287"/>
-      <c r="D14" s="287"/>
-      <c r="E14" s="287"/>
+      <c r="C14" s="284"/>
+      <c r="D14" s="284"/>
+      <c r="E14" s="284"/>
       <c r="F14" s="6">
         <v>1</v>
       </c>
-      <c r="K14" s="289" t="s">
+      <c r="K14" s="299" t="s">
         <v>749</v>
       </c>
-      <c r="L14" s="289"/>
-      <c r="M14" s="289"/>
-      <c r="N14" s="289"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="286"/>
-      <c r="B15" s="287" t="s">
+      <c r="L14" s="299"/>
+      <c r="M14" s="299"/>
+      <c r="N14" s="299"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A15" s="283"/>
+      <c r="B15" s="284" t="s">
         <v>721</v>
       </c>
-      <c r="C15" s="287"/>
-      <c r="D15" s="287"/>
-      <c r="E15" s="287"/>
+      <c r="C15" s="284"/>
+      <c r="D15" s="284"/>
+      <c r="E15" s="284"/>
       <c r="F15" s="6">
         <v>9</v>
       </c>
-      <c r="K15" s="290" t="s">
+      <c r="K15" s="297" t="s">
         <v>1355</v>
       </c>
-      <c r="L15" s="290"/>
-      <c r="M15" s="290"/>
-      <c r="N15" s="290"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="286"/>
-      <c r="B16" s="287" t="s">
+      <c r="L15" s="297"/>
+      <c r="M15" s="297"/>
+      <c r="N15" s="297"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A16" s="283"/>
+      <c r="B16" s="284" t="s">
         <v>723</v>
       </c>
-      <c r="C16" s="287"/>
-      <c r="D16" s="287"/>
-      <c r="E16" s="287"/>
+      <c r="C16" s="284"/>
+      <c r="D16" s="284"/>
+      <c r="E16" s="284"/>
       <c r="F16" s="6">
         <v>28</v>
       </c>
-      <c r="K16" s="301" t="s">
+      <c r="K16" s="288" t="s">
         <v>1356</v>
       </c>
-      <c r="L16" s="301"/>
-      <c r="M16" s="301"/>
-      <c r="N16" s="301"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="286"/>
-      <c r="B17" s="287" t="s">
+      <c r="L16" s="288"/>
+      <c r="M16" s="288"/>
+      <c r="N16" s="288"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A17" s="283"/>
+      <c r="B17" s="284" t="s">
         <v>1355</v>
       </c>
-      <c r="C17" s="287"/>
-      <c r="D17" s="287"/>
-      <c r="E17" s="287"/>
+      <c r="C17" s="284"/>
+      <c r="D17" s="284"/>
+      <c r="E17" s="284"/>
       <c r="F17" s="6">
         <v>3</v>
       </c>
-      <c r="K17" s="302" t="s">
+      <c r="K17" s="289" t="s">
         <v>1357</v>
       </c>
-      <c r="L17" s="302"/>
-      <c r="M17" s="302"/>
-      <c r="N17" s="302"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="286"/>
-      <c r="B18" s="287" t="s">
+      <c r="L17" s="289"/>
+      <c r="M17" s="289"/>
+      <c r="N17" s="289"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A18" s="283"/>
+      <c r="B18" s="284" t="s">
         <v>1356</v>
       </c>
-      <c r="C18" s="287"/>
-      <c r="D18" s="287"/>
-      <c r="E18" s="287"/>
+      <c r="C18" s="284"/>
+      <c r="D18" s="284"/>
+      <c r="E18" s="284"/>
       <c r="F18" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="286"/>
-      <c r="B19" s="287" t="s">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A19" s="283"/>
+      <c r="B19" s="284" t="s">
         <v>1357</v>
       </c>
-      <c r="C19" s="287"/>
-      <c r="D19" s="287"/>
-      <c r="E19" s="287"/>
+      <c r="C19" s="284"/>
+      <c r="D19" s="284"/>
+      <c r="E19" s="284"/>
       <c r="F19" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="298" t="s">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A20" s="285" t="s">
         <v>1363</v>
       </c>
-      <c r="B20" s="287" t="s">
+      <c r="B20" s="284" t="s">
         <v>730</v>
       </c>
-      <c r="C20" s="287"/>
-      <c r="D20" s="287"/>
-      <c r="E20" s="287"/>
+      <c r="C20" s="284"/>
+      <c r="D20" s="284"/>
+      <c r="E20" s="284"/>
       <c r="F20" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="299"/>
-      <c r="B21" s="287" t="s">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A21" s="286"/>
+      <c r="B21" s="284" t="s">
         <v>721</v>
       </c>
-      <c r="C21" s="287"/>
-      <c r="D21" s="287"/>
-      <c r="E21" s="287"/>
+      <c r="C21" s="284"/>
+      <c r="D21" s="284"/>
+      <c r="E21" s="284"/>
       <c r="F21" s="6">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="299"/>
-      <c r="B22" s="287" t="s">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A22" s="286"/>
+      <c r="B22" s="284" t="s">
         <v>723</v>
       </c>
-      <c r="C22" s="287"/>
-      <c r="D22" s="287"/>
-      <c r="E22" s="287"/>
+      <c r="C22" s="284"/>
+      <c r="D22" s="284"/>
+      <c r="E22" s="284"/>
       <c r="F22" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="299"/>
-      <c r="B23" s="287" t="s">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A23" s="286"/>
+      <c r="B23" s="284" t="s">
         <v>1355</v>
       </c>
-      <c r="C23" s="287"/>
-      <c r="D23" s="287"/>
-      <c r="E23" s="287"/>
+      <c r="C23" s="284"/>
+      <c r="D23" s="284"/>
+      <c r="E23" s="284"/>
       <c r="F23" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="300"/>
-      <c r="B24" s="287" t="s">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A24" s="287"/>
+      <c r="B24" s="284" t="s">
         <v>1356</v>
       </c>
-      <c r="C24" s="287"/>
-      <c r="D24" s="287"/>
-      <c r="E24" s="287"/>
+      <c r="C24" s="284"/>
+      <c r="D24" s="284"/>
+      <c r="E24" s="284"/>
       <c r="F24" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="298" t="s">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A25" s="285" t="s">
         <v>1364</v>
       </c>
-      <c r="B25" s="287" t="s">
+      <c r="B25" s="284" t="s">
         <v>730</v>
       </c>
-      <c r="C25" s="287"/>
-      <c r="D25" s="287"/>
-      <c r="E25" s="287"/>
+      <c r="C25" s="284"/>
+      <c r="D25" s="284"/>
+      <c r="E25" s="284"/>
       <c r="F25" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="299"/>
-      <c r="B26" s="287" t="s">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A26" s="286"/>
+      <c r="B26" s="284" t="s">
         <v>721</v>
       </c>
-      <c r="C26" s="287"/>
-      <c r="D26" s="287"/>
-      <c r="E26" s="287"/>
+      <c r="C26" s="284"/>
+      <c r="D26" s="284"/>
+      <c r="E26" s="284"/>
       <c r="F26" s="6">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="299"/>
-      <c r="B27" s="287" t="s">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A27" s="286"/>
+      <c r="B27" s="284" t="s">
         <v>723</v>
       </c>
-      <c r="C27" s="287"/>
-      <c r="D27" s="287"/>
-      <c r="E27" s="287"/>
+      <c r="C27" s="284"/>
+      <c r="D27" s="284"/>
+      <c r="E27" s="284"/>
       <c r="F27" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="300"/>
-      <c r="B28" s="287" t="s">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A28" s="287"/>
+      <c r="B28" s="284" t="s">
         <v>1356</v>
       </c>
-      <c r="C28" s="287"/>
-      <c r="D28" s="287"/>
-      <c r="E28" s="287"/>
+      <c r="C28" s="284"/>
+      <c r="D28" s="284"/>
+      <c r="E28" s="284"/>
       <c r="F28" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="286" t="s">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A29" s="283" t="s">
         <v>12</v>
       </c>
-      <c r="B29" s="287" t="s">
+      <c r="B29" s="284" t="s">
         <v>741</v>
       </c>
-      <c r="C29" s="287"/>
-      <c r="D29" s="287"/>
-      <c r="E29" s="287"/>
+      <c r="C29" s="284"/>
+      <c r="D29" s="284"/>
+      <c r="E29" s="284"/>
       <c r="F29" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="286"/>
-      <c r="B30" s="287" t="s">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A30" s="283"/>
+      <c r="B30" s="284" t="s">
         <v>721</v>
       </c>
-      <c r="C30" s="287"/>
-      <c r="D30" s="287"/>
-      <c r="E30" s="287"/>
+      <c r="C30" s="284"/>
+      <c r="D30" s="284"/>
+      <c r="E30" s="284"/>
       <c r="F30" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="286"/>
-      <c r="B31" s="287" t="s">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A31" s="283"/>
+      <c r="B31" s="284" t="s">
         <v>723</v>
       </c>
-      <c r="C31" s="287"/>
-      <c r="D31" s="287"/>
-      <c r="E31" s="287"/>
+      <c r="C31" s="284"/>
+      <c r="D31" s="284"/>
+      <c r="E31" s="284"/>
       <c r="F31" s="6">
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="286"/>
-      <c r="B32" s="287" t="s">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A32" s="283"/>
+      <c r="B32" s="284" t="s">
         <v>749</v>
       </c>
-      <c r="C32" s="287"/>
-      <c r="D32" s="287"/>
-      <c r="E32" s="287"/>
+      <c r="C32" s="284"/>
+      <c r="D32" s="284"/>
+      <c r="E32" s="284"/>
       <c r="F32" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="286"/>
-      <c r="B33" s="287" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A33" s="283"/>
+      <c r="B33" s="284" t="s">
         <v>1355</v>
       </c>
-      <c r="C33" s="287"/>
-      <c r="D33" s="287"/>
-      <c r="E33" s="287"/>
+      <c r="C33" s="284"/>
+      <c r="D33" s="284"/>
+      <c r="E33" s="284"/>
       <c r="F33" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="286"/>
-      <c r="B34" s="287" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A34" s="283"/>
+      <c r="B34" s="284" t="s">
         <v>1356</v>
       </c>
-      <c r="C34" s="287"/>
-      <c r="D34" s="287"/>
-      <c r="E34" s="287"/>
+      <c r="C34" s="284"/>
+      <c r="D34" s="284"/>
+      <c r="E34" s="284"/>
       <c r="F34" s="6">
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="286"/>
-      <c r="B35" s="287" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A35" s="283"/>
+      <c r="B35" s="284" t="s">
         <v>1357</v>
       </c>
-      <c r="C35" s="287"/>
-      <c r="D35" s="287"/>
-      <c r="E35" s="287"/>
+      <c r="C35" s="284"/>
+      <c r="D35" s="284"/>
+      <c r="E35" s="284"/>
       <c r="F35" s="6">
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="286" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A36" s="283" t="s">
         <v>1365</v>
       </c>
-      <c r="B36" s="287" t="s">
+      <c r="B36" s="284" t="s">
         <v>1360</v>
       </c>
-      <c r="C36" s="287"/>
-      <c r="D36" s="287"/>
-      <c r="E36" s="287"/>
+      <c r="C36" s="284"/>
+      <c r="D36" s="284"/>
+      <c r="E36" s="284"/>
       <c r="F36" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="286"/>
-      <c r="B37" s="287" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A37" s="283"/>
+      <c r="B37" s="284" t="s">
         <v>721</v>
       </c>
-      <c r="C37" s="287"/>
-      <c r="D37" s="287"/>
-      <c r="E37" s="287"/>
+      <c r="C37" s="284"/>
+      <c r="D37" s="284"/>
+      <c r="E37" s="284"/>
       <c r="F37" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="286"/>
-      <c r="B38" s="287" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A38" s="283"/>
+      <c r="B38" s="284" t="s">
         <v>723</v>
       </c>
-      <c r="C38" s="287"/>
-      <c r="D38" s="287"/>
-      <c r="E38" s="287"/>
+      <c r="C38" s="284"/>
+      <c r="D38" s="284"/>
+      <c r="E38" s="284"/>
       <c r="F38" s="6">
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="286"/>
-      <c r="B39" s="287" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A39" s="283"/>
+      <c r="B39" s="284" t="s">
         <v>1356</v>
       </c>
-      <c r="C39" s="287"/>
-      <c r="D39" s="287"/>
-      <c r="E39" s="287"/>
+      <c r="C39" s="284"/>
+      <c r="D39" s="284"/>
+      <c r="E39" s="284"/>
       <c r="F39" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="286" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A40" s="283" t="s">
         <v>20</v>
       </c>
-      <c r="B40" s="287" t="s">
+      <c r="B40" s="284" t="s">
         <v>1360</v>
       </c>
-      <c r="C40" s="287"/>
-      <c r="D40" s="287"/>
-      <c r="E40" s="287"/>
+      <c r="C40" s="284"/>
+      <c r="D40" s="284"/>
+      <c r="E40" s="284"/>
       <c r="F40" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="286"/>
-      <c r="B41" s="287" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A41" s="283"/>
+      <c r="B41" s="284" t="s">
         <v>721</v>
       </c>
-      <c r="C41" s="287"/>
-      <c r="D41" s="287"/>
-      <c r="E41" s="287"/>
+      <c r="C41" s="284"/>
+      <c r="D41" s="284"/>
+      <c r="E41" s="284"/>
       <c r="F41" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="286"/>
-      <c r="B42" s="287" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A42" s="283"/>
+      <c r="B42" s="284" t="s">
         <v>723</v>
       </c>
-      <c r="C42" s="287"/>
-      <c r="D42" s="287"/>
-      <c r="E42" s="287"/>
+      <c r="C42" s="284"/>
+      <c r="D42" s="284"/>
+      <c r="E42" s="284"/>
       <c r="F42" s="6">
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="286"/>
-      <c r="B43" s="287" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A43" s="283"/>
+      <c r="B43" s="284" t="s">
         <v>749</v>
       </c>
-      <c r="C43" s="287"/>
-      <c r="D43" s="287"/>
-      <c r="E43" s="287"/>
+      <c r="C43" s="284"/>
+      <c r="D43" s="284"/>
+      <c r="E43" s="284"/>
       <c r="F43" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="286"/>
-      <c r="B44" s="287" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A44" s="283"/>
+      <c r="B44" s="284" t="s">
         <v>1356</v>
       </c>
-      <c r="C44" s="287"/>
-      <c r="D44" s="287"/>
-      <c r="E44" s="287"/>
+      <c r="C44" s="284"/>
+      <c r="D44" s="284"/>
+      <c r="E44" s="284"/>
       <c r="F44" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="286" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A45" s="283" t="s">
         <v>1366</v>
       </c>
-      <c r="B45" s="287" t="s">
+      <c r="B45" s="284" t="s">
         <v>1360</v>
       </c>
-      <c r="C45" s="287"/>
-      <c r="D45" s="287"/>
-      <c r="E45" s="287"/>
+      <c r="C45" s="284"/>
+      <c r="D45" s="284"/>
+      <c r="E45" s="284"/>
       <c r="F45" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="286"/>
-      <c r="B46" s="287" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A46" s="283"/>
+      <c r="B46" s="284" t="s">
         <v>721</v>
       </c>
-      <c r="C46" s="287"/>
-      <c r="D46" s="287"/>
-      <c r="E46" s="287"/>
+      <c r="C46" s="284"/>
+      <c r="D46" s="284"/>
+      <c r="E46" s="284"/>
       <c r="F46" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="286"/>
-      <c r="B47" s="287" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A47" s="283"/>
+      <c r="B47" s="284" t="s">
         <v>723</v>
       </c>
-      <c r="C47" s="287"/>
-      <c r="D47" s="287"/>
-      <c r="E47" s="287"/>
+      <c r="C47" s="284"/>
+      <c r="D47" s="284"/>
+      <c r="E47" s="284"/>
       <c r="F47" s="6">
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="286"/>
-      <c r="B48" s="287" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A48" s="283"/>
+      <c r="B48" s="284" t="s">
         <v>1356</v>
       </c>
-      <c r="C48" s="287"/>
-      <c r="D48" s="287"/>
-      <c r="E48" s="287"/>
+      <c r="C48" s="284"/>
+      <c r="D48" s="284"/>
+      <c r="E48" s="284"/>
       <c r="F48" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="286"/>
-      <c r="B49" s="287" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A49" s="283"/>
+      <c r="B49" s="284" t="s">
         <v>1357</v>
       </c>
-      <c r="C49" s="287"/>
-      <c r="D49" s="287"/>
-      <c r="E49" s="287"/>
+      <c r="C49" s="284"/>
+      <c r="D49" s="284"/>
+      <c r="E49" s="284"/>
       <c r="F49" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="286" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A50" s="283" t="s">
         <v>1367</v>
       </c>
-      <c r="B50" s="287" t="s">
+      <c r="B50" s="284" t="s">
         <v>1360</v>
       </c>
-      <c r="C50" s="287"/>
-      <c r="D50" s="287"/>
-      <c r="E50" s="287"/>
+      <c r="C50" s="284"/>
+      <c r="D50" s="284"/>
+      <c r="E50" s="284"/>
       <c r="F50" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="286"/>
-      <c r="B51" s="287" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A51" s="283"/>
+      <c r="B51" s="284" t="s">
         <v>721</v>
       </c>
-      <c r="C51" s="287"/>
-      <c r="D51" s="287"/>
-      <c r="E51" s="287"/>
+      <c r="C51" s="284"/>
+      <c r="D51" s="284"/>
+      <c r="E51" s="284"/>
       <c r="F51" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="286"/>
-      <c r="B52" s="287" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A52" s="283"/>
+      <c r="B52" s="284" t="s">
         <v>723</v>
       </c>
-      <c r="C52" s="287"/>
-      <c r="D52" s="287"/>
-      <c r="E52" s="287"/>
+      <c r="C52" s="284"/>
+      <c r="D52" s="284"/>
+      <c r="E52" s="284"/>
       <c r="F52" s="6">
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="286"/>
-      <c r="B53" s="287" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A53" s="283"/>
+      <c r="B53" s="284" t="s">
         <v>1355</v>
       </c>
-      <c r="C53" s="287"/>
-      <c r="D53" s="287"/>
-      <c r="E53" s="287"/>
+      <c r="C53" s="284"/>
+      <c r="D53" s="284"/>
+      <c r="E53" s="284"/>
       <c r="F53" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="286"/>
-      <c r="B54" s="287" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A54" s="283"/>
+      <c r="B54" s="284" t="s">
         <v>1356</v>
       </c>
-      <c r="C54" s="287"/>
-      <c r="D54" s="287"/>
-      <c r="E54" s="287"/>
+      <c r="C54" s="284"/>
+      <c r="D54" s="284"/>
+      <c r="E54" s="284"/>
       <c r="F54" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="286" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A55" s="283" t="s">
         <v>1368</v>
       </c>
-      <c r="B55" s="287" t="s">
+      <c r="B55" s="284" t="s">
         <v>721</v>
       </c>
-      <c r="C55" s="287"/>
-      <c r="D55" s="287"/>
-      <c r="E55" s="287"/>
+      <c r="C55" s="284"/>
+      <c r="D55" s="284"/>
+      <c r="E55" s="284"/>
       <c r="F55" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="286"/>
-      <c r="B56" s="287" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A56" s="283"/>
+      <c r="B56" s="284" t="s">
         <v>723</v>
       </c>
-      <c r="C56" s="287"/>
-      <c r="D56" s="287"/>
-      <c r="E56" s="287"/>
+      <c r="C56" s="284"/>
+      <c r="D56" s="284"/>
+      <c r="E56" s="284"/>
       <c r="F56" s="6">
         <v>27</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="286"/>
-      <c r="B57" s="287" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A57" s="283"/>
+      <c r="B57" s="284" t="s">
         <v>749</v>
       </c>
-      <c r="C57" s="287"/>
-      <c r="D57" s="287"/>
-      <c r="E57" s="287"/>
+      <c r="C57" s="284"/>
+      <c r="D57" s="284"/>
+      <c r="E57" s="284"/>
       <c r="F57" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="286"/>
-      <c r="B58" s="287" t="s">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A58" s="283"/>
+      <c r="B58" s="284" t="s">
         <v>1356</v>
       </c>
-      <c r="C58" s="287"/>
-      <c r="D58" s="287"/>
-      <c r="E58" s="287"/>
+      <c r="C58" s="284"/>
+      <c r="D58" s="284"/>
+      <c r="E58" s="284"/>
       <c r="F58" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="286"/>
-      <c r="B59" s="287" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A59" s="283"/>
+      <c r="B59" s="284" t="s">
         <v>1357</v>
       </c>
-      <c r="C59" s="287"/>
-      <c r="D59" s="287"/>
-      <c r="E59" s="287"/>
+      <c r="C59" s="284"/>
+      <c r="D59" s="284"/>
+      <c r="E59" s="284"/>
       <c r="F59" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="286" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A60" s="283" t="s">
         <v>1369</v>
       </c>
-      <c r="B60" s="287" t="s">
+      <c r="B60" s="284" t="s">
         <v>732</v>
       </c>
-      <c r="C60" s="287"/>
-      <c r="D60" s="287"/>
-      <c r="E60" s="287"/>
+      <c r="C60" s="284"/>
+      <c r="D60" s="284"/>
+      <c r="E60" s="284"/>
       <c r="F60" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="286"/>
-      <c r="B61" s="287" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A61" s="283"/>
+      <c r="B61" s="284" t="s">
         <v>721</v>
       </c>
-      <c r="C61" s="287"/>
-      <c r="D61" s="287"/>
-      <c r="E61" s="287"/>
+      <c r="C61" s="284"/>
+      <c r="D61" s="284"/>
+      <c r="E61" s="284"/>
       <c r="F61" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="286"/>
-      <c r="B62" s="287" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A62" s="283"/>
+      <c r="B62" s="284" t="s">
         <v>723</v>
       </c>
-      <c r="C62" s="287"/>
-      <c r="D62" s="287"/>
-      <c r="E62" s="287"/>
+      <c r="C62" s="284"/>
+      <c r="D62" s="284"/>
+      <c r="E62" s="284"/>
       <c r="F62" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="286"/>
-      <c r="B63" s="287" t="s">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A63" s="283"/>
+      <c r="B63" s="284" t="s">
         <v>1357</v>
       </c>
-      <c r="C63" s="287"/>
-      <c r="D63" s="287"/>
-      <c r="E63" s="287"/>
+      <c r="C63" s="284"/>
+      <c r="D63" s="284"/>
+      <c r="E63" s="284"/>
       <c r="F63" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="286" t="s">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A64" s="283" t="s">
         <v>1370</v>
       </c>
-      <c r="B64" s="287" t="s">
+      <c r="B64" s="284" t="s">
         <v>1360</v>
       </c>
-      <c r="C64" s="287"/>
-      <c r="D64" s="287"/>
-      <c r="E64" s="287"/>
+      <c r="C64" s="284"/>
+      <c r="D64" s="284"/>
+      <c r="E64" s="284"/>
       <c r="F64" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="286"/>
-      <c r="B65" s="287" t="s">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A65" s="283"/>
+      <c r="B65" s="284" t="s">
         <v>721</v>
       </c>
-      <c r="C65" s="287"/>
-      <c r="D65" s="287"/>
-      <c r="E65" s="287"/>
+      <c r="C65" s="284"/>
+      <c r="D65" s="284"/>
+      <c r="E65" s="284"/>
       <c r="F65" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="286"/>
-      <c r="B66" s="287" t="s">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A66" s="283"/>
+      <c r="B66" s="284" t="s">
         <v>723</v>
       </c>
-      <c r="C66" s="287"/>
-      <c r="D66" s="287"/>
-      <c r="E66" s="287"/>
+      <c r="C66" s="284"/>
+      <c r="D66" s="284"/>
+      <c r="E66" s="284"/>
       <c r="F66" s="6">
         <v>41</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="286"/>
-      <c r="B67" s="287" t="s">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A67" s="283"/>
+      <c r="B67" s="284" t="s">
         <v>1355</v>
       </c>
-      <c r="C67" s="287"/>
-      <c r="D67" s="287"/>
-      <c r="E67" s="287"/>
+      <c r="C67" s="284"/>
+      <c r="D67" s="284"/>
+      <c r="E67" s="284"/>
       <c r="F67" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="286"/>
-      <c r="B68" s="287" t="s">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A68" s="283"/>
+      <c r="B68" s="284" t="s">
         <v>1357</v>
       </c>
-      <c r="C68" s="287"/>
-      <c r="D68" s="287"/>
-      <c r="E68" s="287"/>
+      <c r="C68" s="284"/>
+      <c r="D68" s="284"/>
+      <c r="E68" s="284"/>
       <c r="F68" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A69" s="17"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A70" s="17"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A71" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="A64:A68"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B64:E64"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="A25:A28"/>
-    <mergeCell ref="K16:N16"/>
-    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="A50:A54"/>
+    <mergeCell ref="A55:A59"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="A29:A35"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="A40:A44"/>
+    <mergeCell ref="A45:A49"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B42:E42"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B14:E14"/>
@@ -25512,38 +25534,11 @@
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="A29:A35"/>
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="A40:A44"/>
-    <mergeCell ref="A45:A49"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="K17:N17"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B9:E9"/>
@@ -25554,22 +25549,18 @@
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="K13:N13"/>
     <mergeCell ref="K14:N14"/>
-    <mergeCell ref="A50:A54"/>
-    <mergeCell ref="A55:A59"/>
-    <mergeCell ref="A60:A63"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="A64:A68"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B66:E66"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -25578,28 +25569,28 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:R27"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.19921875" customWidth="1"/>
     <col min="2" max="2" width="47.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.59765625" customWidth="1"/>
     <col min="4" max="4" width="24.19921875" customWidth="1"/>
     <col min="5" max="6" width="21.59765625" customWidth="1"/>
-    <col min="7" max="7" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.3984375" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.3984375" style="4" customWidth="1"/>
     <col min="9" max="9" width="16" style="7" customWidth="1"/>
     <col min="10" max="10" width="15" style="19" customWidth="1"/>
-    <col min="11" max="11" width="33.09765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.19921875" style="19" customWidth="1"/>
+    <col min="11" max="11" width="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="30" style="19" customWidth="1"/>
     <col min="13" max="13" width="12.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.19921875" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="50.296875" customWidth="1"/>
-    <col min="17" max="17" width="38.69921875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="50.19921875" customWidth="1"/>
+    <col min="17" max="17" width="38.59765625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="40.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="19" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="19" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="22" t="s">
         <v>520</v>
       </c>
@@ -25655,7 +25646,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="26">
         <v>1</v>
       </c>
@@ -25711,7 +25702,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="34">
         <v>2</v>
       </c>
@@ -25767,7 +25758,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="34">
         <v>3</v>
       </c>
@@ -25823,7 +25814,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="34">
         <v>4</v>
       </c>
@@ -25879,7 +25870,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="34">
         <v>5</v>
       </c>
@@ -25935,7 +25926,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="34">
         <v>6</v>
       </c>
@@ -25991,7 +25982,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="47">
         <v>7</v>
       </c>
@@ -26047,7 +26038,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="47">
         <v>8</v>
       </c>
@@ -26103,7 +26094,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="47">
         <v>9</v>
       </c>
@@ -26159,7 +26150,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="47">
         <v>10</v>
       </c>
@@ -26211,7 +26202,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="47">
         <v>11</v>
       </c>
@@ -26267,7 +26258,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="47">
         <v>12</v>
       </c>
@@ -26323,7 +26314,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="47">
         <v>13</v>
       </c>
@@ -26379,7 +26370,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="47">
         <v>14</v>
       </c>
@@ -26435,7 +26426,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="47">
         <v>15</v>
       </c>
@@ -26491,7 +26482,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="47">
         <v>16</v>
       </c>
@@ -26547,7 +26538,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="47">
         <v>17</v>
       </c>
@@ -26603,7 +26594,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="47">
         <v>18</v>
       </c>
@@ -26659,7 +26650,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="47">
         <v>19</v>
       </c>
@@ -26715,7 +26706,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="47">
         <v>20</v>
       </c>
@@ -26771,7 +26762,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="47">
         <v>21</v>
       </c>
@@ -26827,7 +26818,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="47">
         <v>22</v>
       </c>
@@ -26883,7 +26874,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="47">
         <v>23</v>
       </c>
@@ -26939,7 +26930,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="47">
         <v>24</v>
       </c>
@@ -26995,7 +26986,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="58">
         <v>25</v>
       </c>
@@ -27051,7 +27042,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="182">
         <v>26</v>
       </c>
@@ -27097,7 +27088,7 @@
       <c r="O27" s="185">
         <v>15</v>
       </c>
-      <c r="P27" s="254" t="s">
+      <c r="P27" s="251" t="s">
         <v>1437</v>
       </c>
       <c r="Q27" s="186" t="s">
@@ -27116,7 +27107,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:R32"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.19921875" style="1" customWidth="1"/>
     <col min="2" max="2" width="47.59765625" style="21" bestFit="1" customWidth="1"/>
@@ -27124,21 +27115,21 @@
     <col min="4" max="4" width="24.19921875" style="21" customWidth="1"/>
     <col min="5" max="5" width="21.59765625" style="21" customWidth="1"/>
     <col min="6" max="6" width="21.59765625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="13.296875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="13.19921875" style="5" customWidth="1"/>
     <col min="8" max="8" width="14.3984375" style="5" customWidth="1"/>
     <col min="9" max="9" width="16" style="7" customWidth="1"/>
     <col min="10" max="10" width="13.3984375" customWidth="1"/>
-    <col min="11" max="11" width="26.09765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26" style="5" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.19921875" customWidth="1"/>
     <col min="13" max="13" width="16.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="56.296875" customWidth="1"/>
+    <col min="14" max="14" width="25.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.19921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="56.19921875" customWidth="1"/>
     <col min="17" max="17" width="38.3984375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="40" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="19" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="19" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="22" t="s">
         <v>520</v>
       </c>
@@ -27194,7 +27185,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="26">
         <v>1</v>
       </c>
@@ -27250,7 +27241,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="34">
         <v>2</v>
       </c>
@@ -27306,7 +27297,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="34">
         <v>3</v>
       </c>
@@ -27362,7 +27353,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="34">
         <v>5</v>
       </c>
@@ -27372,7 +27363,7 @@
       <c r="C5" s="88" t="s">
         <v>306</v>
       </c>
-      <c r="D5" s="283" t="s">
+      <c r="D5" s="280" t="s">
         <v>1494</v>
       </c>
       <c r="E5" s="88" t="s">
@@ -27418,7 +27409,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="40">
         <v>6</v>
       </c>
@@ -27474,7 +27465,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="40">
         <v>7</v>
       </c>
@@ -27530,7 +27521,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="40">
         <v>8</v>
       </c>
@@ -27586,7 +27577,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="40">
         <v>9</v>
       </c>
@@ -27642,7 +27633,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="40">
         <v>10</v>
       </c>
@@ -27698,7 +27689,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="40">
         <v>11</v>
       </c>
@@ -27754,7 +27745,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="40">
         <v>12</v>
       </c>
@@ -27810,7 +27801,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="40">
         <v>13</v>
       </c>
@@ -27866,7 +27857,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="40">
         <v>14</v>
       </c>
@@ -27922,7 +27913,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="40">
         <v>15</v>
       </c>
@@ -27978,7 +27969,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="40">
         <v>16</v>
       </c>
@@ -28034,7 +28025,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="40">
         <v>17</v>
       </c>
@@ -28090,7 +28081,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="40">
         <v>18</v>
       </c>
@@ -28142,7 +28133,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="40">
         <v>19</v>
       </c>
@@ -28198,7 +28189,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="40">
         <v>20</v>
       </c>
@@ -28254,7 +28245,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="40">
         <v>21</v>
       </c>
@@ -28310,7 +28301,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="40">
         <v>22</v>
       </c>
@@ -28366,7 +28357,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="40">
         <v>23</v>
       </c>
@@ -28422,7 +28413,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="40">
         <v>24</v>
       </c>
@@ -28478,7 +28469,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="40">
         <v>25</v>
       </c>
@@ -28534,7 +28525,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="40">
         <v>26</v>
       </c>
@@ -28590,7 +28581,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="40">
         <v>27</v>
       </c>
@@ -28646,7 +28637,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="40">
         <v>28</v>
       </c>
@@ -28702,7 +28693,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="52">
         <v>29</v>
       </c>
@@ -28748,7 +28739,7 @@
       <c r="O29" s="56">
         <v>1</v>
       </c>
-      <c r="P29" s="253" t="s">
+      <c r="P29" s="250" t="s">
         <v>748</v>
       </c>
       <c r="Q29" s="58" t="s">
@@ -28758,7 +28749,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="52">
         <v>30</v>
       </c>
@@ -28804,17 +28795,17 @@
       <c r="O30" s="56">
         <v>1</v>
       </c>
-      <c r="P30" s="245" t="s">
+      <c r="P30" s="242" t="s">
         <v>1443</v>
       </c>
-      <c r="Q30" s="246" t="s">
+      <c r="Q30" s="243" t="s">
         <v>718</v>
       </c>
-      <c r="R30" s="246" t="s">
+      <c r="R30" s="243" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="52">
         <v>31</v>
       </c>
@@ -28860,17 +28851,17 @@
       <c r="O31" s="56">
         <v>2</v>
       </c>
-      <c r="P31" s="245" t="s">
+      <c r="P31" s="242" t="s">
         <v>1443</v>
       </c>
-      <c r="Q31" s="246" t="s">
+      <c r="Q31" s="243" t="s">
         <v>718</v>
       </c>
-      <c r="R31" s="246" t="s">
+      <c r="R31" s="243" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="190">
         <v>32</v>
       </c>
@@ -28935,29 +28926,29 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:R42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.19921875" style="16" customWidth="1"/>
     <col min="2" max="2" width="46.19921875" style="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.59765625" style="25" customWidth="1"/>
     <col min="4" max="4" width="24.19921875" style="25" customWidth="1"/>
     <col min="5" max="6" width="21.59765625" style="25" customWidth="1"/>
-    <col min="7" max="7" width="13.296875" style="25" customWidth="1"/>
+    <col min="7" max="7" width="13.19921875" style="25" customWidth="1"/>
     <col min="8" max="8" width="14.3984375" style="25" customWidth="1"/>
     <col min="9" max="9" width="16" style="9" customWidth="1"/>
     <col min="10" max="10" width="13.796875" style="8" customWidth="1"/>
-    <col min="11" max="11" width="30.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.19921875" style="8" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.796875" style="8" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" style="9" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19" style="9" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.796875" style="9" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="49.296875" style="8" customWidth="1"/>
+    <col min="16" max="16" width="49.19921875" style="8" customWidth="1"/>
     <col min="17" max="17" width="38.3984375" style="8" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="39.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="8.796875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="15" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="15" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="22" t="s">
         <v>520</v>
       </c>
@@ -29013,14 +29004,14 @@
         <v>717</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="26">
         <v>1</v>
       </c>
-      <c r="B2" s="251" t="s">
+      <c r="B2" s="248" t="s">
         <v>1461</v>
       </c>
-      <c r="C2" s="284" t="s">
+      <c r="C2" s="281" t="s">
         <v>1367</v>
       </c>
       <c r="D2" s="147" t="s">
@@ -29069,14 +29060,14 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="34">
         <v>2</v>
       </c>
       <c r="B3" s="88" t="s">
         <v>1084</v>
       </c>
-      <c r="C3" s="283" t="s">
+      <c r="C3" s="280" t="s">
         <v>1367</v>
       </c>
       <c r="D3" s="88" t="s">
@@ -29125,17 +29116,17 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="34">
         <v>3</v>
       </c>
       <c r="B4" s="88" t="s">
         <v>1085</v>
       </c>
-      <c r="C4" s="283" t="s">
+      <c r="C4" s="280" t="s">
         <v>1367</v>
       </c>
-      <c r="D4" s="283" t="s">
+      <c r="D4" s="280" t="s">
         <v>1367</v>
       </c>
       <c r="E4" s="88" t="s">
@@ -29181,14 +29172,14 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="34">
         <v>4</v>
       </c>
       <c r="B5" s="88" t="s">
         <v>1086</v>
       </c>
-      <c r="C5" s="283" t="s">
+      <c r="C5" s="280" t="s">
         <v>1367</v>
       </c>
       <c r="D5" s="88" t="s">
@@ -29237,14 +29228,14 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="34">
         <v>5</v>
       </c>
       <c r="B6" s="88" t="s">
         <v>1087</v>
       </c>
-      <c r="C6" s="283" t="s">
+      <c r="C6" s="280" t="s">
         <v>1367</v>
       </c>
       <c r="D6" s="88" t="s">
@@ -29293,14 +29284,14 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="40">
         <v>6</v>
       </c>
       <c r="B7" s="162" t="s">
         <v>1056</v>
       </c>
-      <c r="C7" s="285" t="s">
+      <c r="C7" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D7" s="162" t="s">
@@ -29349,14 +29340,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="40">
         <v>7</v>
       </c>
       <c r="B8" s="162" t="s">
         <v>1057</v>
       </c>
-      <c r="C8" s="285" t="s">
+      <c r="C8" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D8" s="162" t="s">
@@ -29405,14 +29396,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="40">
         <v>8</v>
       </c>
       <c r="B9" s="162" t="s">
         <v>1058</v>
       </c>
-      <c r="C9" s="285" t="s">
+      <c r="C9" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D9" s="162" t="s">
@@ -29461,14 +29452,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="40">
         <v>9</v>
       </c>
       <c r="B10" s="162" t="s">
         <v>1059</v>
       </c>
-      <c r="C10" s="285" t="s">
+      <c r="C10" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D10" s="162" t="s">
@@ -29517,14 +29508,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="40">
         <v>10</v>
       </c>
       <c r="B11" s="162" t="s">
         <v>1060</v>
       </c>
-      <c r="C11" s="285" t="s">
+      <c r="C11" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D11" s="162" t="s">
@@ -29573,17 +29564,17 @@
         <v>516</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="40">
         <v>11</v>
       </c>
       <c r="B12" s="162" t="s">
         <v>1061</v>
       </c>
-      <c r="C12" s="285" t="s">
+      <c r="C12" s="282" t="s">
         <v>1367</v>
       </c>
-      <c r="D12" s="285" t="s">
+      <c r="D12" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="E12" s="162" t="s">
@@ -29629,17 +29620,17 @@
         <v>516</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="40">
         <v>12</v>
       </c>
       <c r="B13" s="162" t="s">
         <v>1062</v>
       </c>
-      <c r="C13" s="285" t="s">
+      <c r="C13" s="282" t="s">
         <v>1367</v>
       </c>
-      <c r="D13" s="285" t="s">
+      <c r="D13" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="E13" s="162" t="s">
@@ -29685,17 +29676,17 @@
         <v>516</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="40">
         <v>13</v>
       </c>
       <c r="B14" s="162" t="s">
         <v>1063</v>
       </c>
-      <c r="C14" s="285" t="s">
+      <c r="C14" s="282" t="s">
         <v>1367</v>
       </c>
-      <c r="D14" s="285" t="s">
+      <c r="D14" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="E14" s="162" t="s">
@@ -29741,17 +29732,17 @@
         <v>516</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="40">
         <v>14</v>
       </c>
       <c r="B15" s="162" t="s">
         <v>1064</v>
       </c>
-      <c r="C15" s="285" t="s">
+      <c r="C15" s="282" t="s">
         <v>1367</v>
       </c>
-      <c r="D15" s="285" t="s">
+      <c r="D15" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="E15" s="162" t="s">
@@ -29797,17 +29788,17 @@
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="40">
         <v>15</v>
       </c>
       <c r="B16" s="162" t="s">
         <v>1065</v>
       </c>
-      <c r="C16" s="285" t="s">
+      <c r="C16" s="282" t="s">
         <v>1367</v>
       </c>
-      <c r="D16" s="285" t="s">
+      <c r="D16" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="E16" s="162" t="s">
@@ -29853,17 +29844,17 @@
         <v>516</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="40">
         <v>16</v>
       </c>
       <c r="B17" s="162" t="s">
         <v>1066</v>
       </c>
-      <c r="C17" s="285" t="s">
+      <c r="C17" s="282" t="s">
         <v>1367</v>
       </c>
-      <c r="D17" s="285" t="s">
+      <c r="D17" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="E17" s="162" t="s">
@@ -29909,17 +29900,17 @@
         <v>516</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="40">
         <v>17</v>
       </c>
       <c r="B18" s="162" t="s">
         <v>1067</v>
       </c>
-      <c r="C18" s="285" t="s">
+      <c r="C18" s="282" t="s">
         <v>1367</v>
       </c>
-      <c r="D18" s="285" t="s">
+      <c r="D18" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="E18" s="162" t="s">
@@ -29965,14 +29956,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="40">
         <v>18</v>
       </c>
       <c r="B19" s="162" t="s">
         <v>1068</v>
       </c>
-      <c r="C19" s="285" t="s">
+      <c r="C19" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D19" s="162" t="s">
@@ -30021,14 +30012,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="40">
         <v>19</v>
       </c>
       <c r="B20" s="162" t="s">
         <v>1069</v>
       </c>
-      <c r="C20" s="285" t="s">
+      <c r="C20" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D20" s="162" t="s">
@@ -30077,14 +30068,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="40">
         <v>20</v>
       </c>
       <c r="B21" s="162" t="s">
         <v>1070</v>
       </c>
-      <c r="C21" s="285" t="s">
+      <c r="C21" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D21" s="162" t="s">
@@ -30133,14 +30124,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="40">
         <v>21</v>
       </c>
       <c r="B22" s="162" t="s">
         <v>1071</v>
       </c>
-      <c r="C22" s="285" t="s">
+      <c r="C22" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D22" s="162" t="s">
@@ -30189,14 +30180,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="40">
         <v>22</v>
       </c>
       <c r="B23" s="162" t="s">
         <v>1072</v>
       </c>
-      <c r="C23" s="285" t="s">
+      <c r="C23" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D23" s="162" t="s">
@@ -30245,14 +30236,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="40">
         <v>23</v>
       </c>
       <c r="B24" s="162" t="s">
         <v>1073</v>
       </c>
-      <c r="C24" s="285" t="s">
+      <c r="C24" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D24" s="162" t="s">
@@ -30301,14 +30292,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="40">
         <v>24</v>
       </c>
       <c r="B25" s="162" t="s">
         <v>1074</v>
       </c>
-      <c r="C25" s="285" t="s">
+      <c r="C25" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D25" s="162" t="s">
@@ -30357,14 +30348,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="40">
         <v>25</v>
       </c>
       <c r="B26" s="162" t="s">
         <v>1075</v>
       </c>
-      <c r="C26" s="285" t="s">
+      <c r="C26" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D26" s="162" t="s">
@@ -30413,14 +30404,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="40">
         <v>26</v>
       </c>
       <c r="B27" s="162" t="s">
         <v>1076</v>
       </c>
-      <c r="C27" s="285" t="s">
+      <c r="C27" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D27" s="162" t="s">
@@ -30469,14 +30460,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="40">
         <v>27</v>
       </c>
       <c r="B28" s="162" t="s">
         <v>1077</v>
       </c>
-      <c r="C28" s="285" t="s">
+      <c r="C28" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D28" s="162" t="s">
@@ -30525,14 +30516,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="40">
         <v>28</v>
       </c>
       <c r="B29" s="162" t="s">
         <v>1078</v>
       </c>
-      <c r="C29" s="285" t="s">
+      <c r="C29" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D29" s="162" t="s">
@@ -30581,14 +30572,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="40">
         <v>29</v>
       </c>
       <c r="B30" s="162" t="s">
         <v>1079</v>
       </c>
-      <c r="C30" s="285" t="s">
+      <c r="C30" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D30" s="162" t="s">
@@ -30637,14 +30628,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="40">
         <v>30</v>
       </c>
       <c r="B31" s="162" t="s">
         <v>1080</v>
       </c>
-      <c r="C31" s="285" t="s">
+      <c r="C31" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D31" s="162" t="s">
@@ -30693,14 +30684,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="40">
         <v>31</v>
       </c>
       <c r="B32" s="162" t="s">
         <v>1081</v>
       </c>
-      <c r="C32" s="285" t="s">
+      <c r="C32" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D32" s="162" t="s">
@@ -30749,14 +30740,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="40">
         <v>32</v>
       </c>
       <c r="B33" s="162" t="s">
         <v>1082</v>
       </c>
-      <c r="C33" s="285" t="s">
+      <c r="C33" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D33" s="162" t="s">
@@ -30805,14 +30796,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="40">
         <v>33</v>
       </c>
       <c r="B34" s="162" t="s">
         <v>1083</v>
       </c>
-      <c r="C34" s="285" t="s">
+      <c r="C34" s="282" t="s">
         <v>1367</v>
       </c>
       <c r="D34" s="162" t="s">
@@ -30861,7 +30852,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="59">
         <v>34</v>
       </c>
@@ -30917,7 +30908,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="52">
         <v>35</v>
       </c>
@@ -30966,14 +30957,14 @@
       <c r="P36" s="219" t="s">
         <v>1448</v>
       </c>
-      <c r="Q36" s="246" t="s">
+      <c r="Q36" s="243" t="s">
         <v>718</v>
       </c>
-      <c r="R36" s="246" t="s">
+      <c r="R36" s="243" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="52">
         <v>36</v>
       </c>
@@ -31022,14 +31013,14 @@
       <c r="P37" s="219" t="s">
         <v>1448</v>
       </c>
-      <c r="Q37" s="246" t="s">
+      <c r="Q37" s="243" t="s">
         <v>718</v>
       </c>
-      <c r="R37" s="246" t="s">
+      <c r="R37" s="243" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="52">
         <v>37</v>
       </c>
@@ -31085,10 +31076,10 @@
         <v>699</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="41" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="42" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <autoFilter ref="A1:R38" xr:uid="{00000000-0001-0000-0E00-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -31098,29 +31089,29 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:R37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.19921875" style="16" customWidth="1"/>
     <col min="2" max="2" width="43.59765625" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.69921875" style="17" customWidth="1"/>
+    <col min="3" max="3" width="12.59765625" style="17" customWidth="1"/>
     <col min="4" max="4" width="24.19921875" style="17" customWidth="1"/>
     <col min="5" max="6" width="21.59765625" style="15" customWidth="1"/>
-    <col min="7" max="7" width="13.296875" style="18" customWidth="1"/>
+    <col min="7" max="7" width="13.19921875" style="18" customWidth="1"/>
     <col min="8" max="8" width="14.3984375" style="18" customWidth="1"/>
     <col min="9" max="9" width="16" style="16" customWidth="1"/>
     <col min="10" max="10" width="14" style="15" customWidth="1"/>
-    <col min="11" max="11" width="30.8984375" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.796875" style="15" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.19921875" style="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.69921875" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.59765625" style="16" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.796875" style="16" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.296875" style="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="55.8984375" style="15" customWidth="1"/>
+    <col min="15" max="15" width="11.19921875" style="16" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="55.796875" style="15" customWidth="1"/>
     <col min="17" max="17" width="38.3984375" style="15" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="39.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="8.796875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="15" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="15" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="22" t="s">
         <v>520</v>
       </c>
@@ -31176,7 +31167,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="34">
         <v>1</v>
       </c>
@@ -31232,7 +31223,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="34">
         <v>2</v>
       </c>
@@ -31242,7 +31233,7 @@
       <c r="C3" s="88" t="s">
         <v>1368</v>
       </c>
-      <c r="D3" s="283" t="s">
+      <c r="D3" s="280" t="s">
         <v>1368</v>
       </c>
       <c r="E3" s="35" t="s">
@@ -31288,7 +31279,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="34">
         <v>3</v>
       </c>
@@ -31344,7 +31335,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="40">
         <v>4</v>
       </c>
@@ -31393,14 +31384,14 @@
       <c r="P5" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q5" s="241" t="s">
+      <c r="Q5" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R5" s="241" t="s">
+      <c r="R5" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="40">
         <v>5</v>
       </c>
@@ -31449,14 +31440,14 @@
       <c r="P6" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q6" s="241" t="s">
+      <c r="Q6" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R6" s="241" t="s">
+      <c r="R6" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="40">
         <v>6</v>
       </c>
@@ -31505,14 +31496,14 @@
       <c r="P7" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q7" s="241" t="s">
+      <c r="Q7" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R7" s="241" t="s">
+      <c r="R7" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="40">
         <v>7</v>
       </c>
@@ -31561,14 +31552,14 @@
       <c r="P8" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q8" s="241" t="s">
+      <c r="Q8" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R8" s="241" t="s">
+      <c r="R8" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="40">
         <v>8</v>
       </c>
@@ -31617,14 +31608,14 @@
       <c r="P9" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q9" s="241" t="s">
+      <c r="Q9" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R9" s="241" t="s">
+      <c r="R9" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="40">
         <v>9</v>
       </c>
@@ -31673,14 +31664,14 @@
       <c r="P10" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q10" s="241" t="s">
+      <c r="Q10" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R10" s="241" t="s">
+      <c r="R10" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="40">
         <v>10</v>
       </c>
@@ -31729,14 +31720,14 @@
       <c r="P11" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q11" s="241" t="s">
+      <c r="Q11" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R11" s="241" t="s">
+      <c r="R11" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="40">
         <v>11</v>
       </c>
@@ -31785,14 +31776,14 @@
       <c r="P12" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q12" s="241" t="s">
+      <c r="Q12" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R12" s="241" t="s">
+      <c r="R12" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="40">
         <v>12</v>
       </c>
@@ -31841,14 +31832,14 @@
       <c r="P13" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q13" s="241" t="s">
+      <c r="Q13" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R13" s="241" t="s">
+      <c r="R13" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="40">
         <v>13</v>
       </c>
@@ -31897,14 +31888,14 @@
       <c r="P14" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q14" s="241" t="s">
+      <c r="Q14" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R14" s="241" t="s">
+      <c r="R14" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="40">
         <v>14</v>
       </c>
@@ -31953,14 +31944,14 @@
       <c r="P15" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q15" s="241" t="s">
+      <c r="Q15" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R15" s="241" t="s">
+      <c r="R15" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="40">
         <v>15</v>
       </c>
@@ -32009,14 +32000,14 @@
       <c r="P16" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q16" s="241" t="s">
+      <c r="Q16" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R16" s="241" t="s">
+      <c r="R16" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="40">
         <v>16</v>
       </c>
@@ -32065,14 +32056,14 @@
       <c r="P17" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q17" s="241" t="s">
+      <c r="Q17" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R17" s="241" t="s">
+      <c r="R17" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="40">
         <v>17</v>
       </c>
@@ -32121,14 +32112,14 @@
       <c r="P18" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q18" s="241" t="s">
+      <c r="Q18" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R18" s="241" t="s">
+      <c r="R18" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="40">
         <v>18</v>
       </c>
@@ -32177,14 +32168,14 @@
       <c r="P19" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q19" s="241" t="s">
+      <c r="Q19" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R19" s="241" t="s">
+      <c r="R19" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="40">
         <v>19</v>
       </c>
@@ -32233,14 +32224,14 @@
       <c r="P20" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q20" s="241" t="s">
+      <c r="Q20" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R20" s="241" t="s">
+      <c r="R20" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="40">
         <v>20</v>
       </c>
@@ -32289,14 +32280,14 @@
       <c r="P21" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q21" s="241" t="s">
+      <c r="Q21" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R21" s="241" t="s">
+      <c r="R21" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="40">
         <v>21</v>
       </c>
@@ -32345,14 +32336,14 @@
       <c r="P22" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q22" s="241" t="s">
+      <c r="Q22" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R22" s="241" t="s">
+      <c r="R22" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="40">
         <v>22</v>
       </c>
@@ -32401,14 +32392,14 @@
       <c r="P23" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q23" s="241" t="s">
+      <c r="Q23" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R23" s="241" t="s">
+      <c r="R23" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="40">
         <v>23</v>
       </c>
@@ -32457,14 +32448,14 @@
       <c r="P24" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q24" s="241" t="s">
+      <c r="Q24" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R24" s="241" t="s">
+      <c r="R24" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="40">
         <v>24</v>
       </c>
@@ -32513,14 +32504,14 @@
       <c r="P25" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q25" s="241" t="s">
+      <c r="Q25" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R25" s="241" t="s">
+      <c r="R25" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="40">
         <v>25</v>
       </c>
@@ -32569,14 +32560,14 @@
       <c r="P26" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q26" s="241" t="s">
+      <c r="Q26" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R26" s="241" t="s">
+      <c r="R26" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="40">
         <v>26</v>
       </c>
@@ -32625,14 +32616,14 @@
       <c r="P27" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q27" s="241" t="s">
+      <c r="Q27" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R27" s="241" t="s">
+      <c r="R27" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="40">
         <v>27</v>
       </c>
@@ -32681,14 +32672,14 @@
       <c r="P28" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q28" s="241" t="s">
+      <c r="Q28" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R28" s="241" t="s">
+      <c r="R28" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="40">
         <v>28</v>
       </c>
@@ -32737,14 +32728,14 @@
       <c r="P29" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q29" s="241" t="s">
+      <c r="Q29" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R29" s="241" t="s">
+      <c r="R29" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="40">
         <v>29</v>
       </c>
@@ -32793,14 +32784,14 @@
       <c r="P30" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q30" s="241" t="s">
+      <c r="Q30" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R30" s="241" t="s">
+      <c r="R30" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="40">
         <v>30</v>
       </c>
@@ -32849,21 +32840,21 @@
       <c r="P31" s="221" t="s">
         <v>1451</v>
       </c>
-      <c r="Q31" s="241" t="s">
+      <c r="Q31" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R31" s="241" t="s">
+      <c r="R31" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="52">
         <v>31</v>
       </c>
       <c r="B32" s="172" t="s">
         <v>1118</v>
       </c>
-      <c r="C32" s="281" t="s">
+      <c r="C32" s="278" t="s">
         <v>1368</v>
       </c>
       <c r="D32" s="150" t="s">
@@ -32912,14 +32903,14 @@
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="52">
         <v>32</v>
       </c>
       <c r="B33" s="150" t="s">
         <v>1119</v>
       </c>
-      <c r="C33" s="281" t="s">
+      <c r="C33" s="278" t="s">
         <v>1368</v>
       </c>
       <c r="D33" s="150" t="s">
@@ -32958,7 +32949,7 @@
       <c r="O33" s="56">
         <v>1</v>
       </c>
-      <c r="P33" s="245" t="s">
+      <c r="P33" s="242" t="s">
         <v>1453</v>
       </c>
       <c r="Q33" s="58" t="s">
@@ -32968,14 +32959,14 @@
         <v>700</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="52">
         <v>33</v>
       </c>
       <c r="B34" s="150" t="s">
         <v>1120</v>
       </c>
-      <c r="C34" s="281" t="s">
+      <c r="C34" s="278" t="s">
         <v>1368</v>
       </c>
       <c r="D34" s="150" t="s">
@@ -33024,7 +33015,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="190">
         <v>34</v>
       </c>
@@ -33070,7 +33061,7 @@
       <c r="O35" s="125">
         <v>0</v>
       </c>
-      <c r="P35" s="255" t="s">
+      <c r="P35" s="252" t="s">
         <v>719</v>
       </c>
       <c r="Q35" s="201" t="s">
@@ -33080,7 +33071,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="190">
         <v>35</v>
       </c>
@@ -33126,7 +33117,7 @@
       <c r="O36" s="125">
         <v>0</v>
       </c>
-      <c r="P36" s="255" t="s">
+      <c r="P36" s="252" t="s">
         <v>719</v>
       </c>
       <c r="Q36" s="201" t="s">
@@ -33136,14 +33127,14 @@
         <v>516</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="185">
         <v>36</v>
       </c>
       <c r="B37" s="186" t="s">
         <v>1123</v>
       </c>
-      <c r="C37" s="282" t="s">
+      <c r="C37" s="279" t="s">
         <v>1368</v>
       </c>
       <c r="D37" s="186" t="s">
@@ -33182,7 +33173,7 @@
       <c r="O37" s="185">
         <v>83</v>
       </c>
-      <c r="P37" s="256" t="s">
+      <c r="P37" s="253" t="s">
         <v>750</v>
       </c>
       <c r="Q37" s="182" t="s">
@@ -33201,28 +33192,28 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:R38"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.19921875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="39.296875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="39.19921875" style="5" customWidth="1"/>
     <col min="3" max="3" width="13.796875" style="5" customWidth="1"/>
     <col min="4" max="4" width="24.19921875" style="5" customWidth="1"/>
     <col min="5" max="6" width="21.59765625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="13.296875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="13.19921875" style="5" customWidth="1"/>
     <col min="8" max="8" width="14.3984375" style="4" customWidth="1"/>
     <col min="9" max="9" width="16" style="7" customWidth="1"/>
     <col min="10" max="10" width="13.3984375" customWidth="1"/>
-    <col min="11" max="11" width="25.09765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.296875" customWidth="1"/>
-    <col min="13" max="13" width="11.69921875" style="7" customWidth="1"/>
+    <col min="11" max="11" width="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.19921875" customWidth="1"/>
+    <col min="13" max="13" width="11.59765625" style="7" customWidth="1"/>
     <col min="14" max="14" width="18.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.19921875" style="7" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="55.3984375" customWidth="1"/>
     <col min="17" max="17" width="38.3984375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="39.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="22" t="s">
         <v>520</v>
       </c>
@@ -33278,7 +33269,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="204">
         <v>1</v>
       </c>
@@ -33334,7 +33325,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="208">
         <v>2</v>
       </c>
@@ -33383,14 +33374,14 @@
       <c r="P3" s="218" t="s">
         <v>1457</v>
       </c>
-      <c r="Q3" s="257" t="s">
+      <c r="Q3" s="254" t="s">
         <v>1397</v>
       </c>
-      <c r="R3" s="257" t="s">
+      <c r="R3" s="254" t="s">
         <v>1404</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="208">
         <v>3</v>
       </c>
@@ -33439,14 +33430,14 @@
       <c r="P4" s="218" t="s">
         <v>1457</v>
       </c>
-      <c r="Q4" s="257" t="s">
+      <c r="Q4" s="254" t="s">
         <v>1397</v>
       </c>
-      <c r="R4" s="257" t="s">
+      <c r="R4" s="254" t="s">
         <v>1404</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="208">
         <v>4</v>
       </c>
@@ -33495,14 +33486,14 @@
       <c r="P5" s="218" t="s">
         <v>1457</v>
       </c>
-      <c r="Q5" s="257" t="s">
+      <c r="Q5" s="254" t="s">
         <v>1397</v>
       </c>
-      <c r="R5" s="257" t="s">
+      <c r="R5" s="254" t="s">
         <v>1404</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="208">
         <v>5</v>
       </c>
@@ -33551,14 +33542,14 @@
       <c r="P6" s="218" t="s">
         <v>1457</v>
       </c>
-      <c r="Q6" s="257" t="s">
+      <c r="Q6" s="254" t="s">
         <v>1397</v>
       </c>
-      <c r="R6" s="257" t="s">
+      <c r="R6" s="254" t="s">
         <v>1404</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="208">
         <v>6</v>
       </c>
@@ -33607,14 +33598,14 @@
       <c r="P7" s="218" t="s">
         <v>1457</v>
       </c>
-      <c r="Q7" s="257" t="s">
+      <c r="Q7" s="254" t="s">
         <v>1397</v>
       </c>
-      <c r="R7" s="257" t="s">
+      <c r="R7" s="254" t="s">
         <v>1404</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="209">
         <v>7</v>
       </c>
@@ -33670,7 +33661,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="209">
         <v>8</v>
       </c>
@@ -33726,7 +33717,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="209">
         <v>9</v>
       </c>
@@ -33782,7 +33773,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="209">
         <v>10</v>
       </c>
@@ -33838,7 +33829,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="209">
         <v>11</v>
       </c>
@@ -33894,7 +33885,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="209">
         <v>12</v>
       </c>
@@ -33950,7 +33941,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="209">
         <v>13</v>
       </c>
@@ -34006,7 +33997,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="209">
         <v>14</v>
       </c>
@@ -34062,7 +34053,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="209">
         <v>15</v>
       </c>
@@ -34118,7 +34109,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="209">
         <v>16</v>
       </c>
@@ -34174,7 +34165,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="209">
         <v>17</v>
       </c>
@@ -34230,7 +34221,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="209">
         <v>18</v>
       </c>
@@ -34286,7 +34277,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="209">
         <v>19</v>
       </c>
@@ -34342,7 +34333,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="209">
         <v>20</v>
       </c>
@@ -34398,7 +34389,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="209">
         <v>21</v>
       </c>
@@ -34454,7 +34445,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="209">
         <v>22</v>
       </c>
@@ -34510,7 +34501,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="209">
         <v>23</v>
       </c>
@@ -34566,7 +34557,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="209">
         <v>24</v>
       </c>
@@ -34622,7 +34613,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="209">
         <v>25</v>
       </c>
@@ -34678,7 +34669,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="209">
         <v>26</v>
       </c>
@@ -34734,7 +34725,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="210">
         <v>27</v>
       </c>
@@ -34790,7 +34781,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="210">
         <v>28</v>
       </c>
@@ -34846,15 +34837,15 @@
         <v>575</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="35" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="31" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="33" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="34" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="35" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="36" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="37" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="38" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <autoFilter ref="A1:R29" xr:uid="{00000000-0001-0000-1000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -34864,29 +34855,29 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:R49"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="4.69921875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="52.69921875" style="21" customWidth="1"/>
-    <col min="3" max="3" width="13.5" style="19" customWidth="1"/>
+    <col min="1" max="1" width="4.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="52.59765625" style="21" customWidth="1"/>
+    <col min="3" max="3" width="13.3984375" style="19" customWidth="1"/>
     <col min="4" max="4" width="24.19921875" style="19" customWidth="1"/>
-    <col min="5" max="5" width="17.296875" style="19" customWidth="1"/>
+    <col min="5" max="5" width="17.19921875" style="19" customWidth="1"/>
     <col min="6" max="6" width="28.19921875" style="19" customWidth="1"/>
     <col min="7" max="7" width="11.796875" style="21" customWidth="1"/>
-    <col min="8" max="8" width="13.296875" style="20" customWidth="1"/>
-    <col min="9" max="9" width="15.296875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.19921875" style="20" customWidth="1"/>
+    <col min="9" max="9" width="15.19921875" style="1" customWidth="1"/>
     <col min="10" max="10" width="14.3984375" style="19" customWidth="1"/>
-    <col min="11" max="11" width="30.296875" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.19921875" style="19" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.19921875" style="19" customWidth="1"/>
-    <col min="13" max="13" width="11.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.796875" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="49.8984375" customWidth="1"/>
+    <col min="16" max="16" width="49.796875" customWidth="1"/>
     <col min="17" max="17" width="38.59765625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="39.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="19" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="19" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="22" t="s">
         <v>520</v>
       </c>
@@ -34942,11 +34933,11 @@
         <v>717</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="26">
         <v>1</v>
       </c>
-      <c r="B2" s="251" t="s">
+      <c r="B2" s="248" t="s">
         <v>1458</v>
       </c>
       <c r="C2" s="28" t="s">
@@ -34998,7 +34989,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="34">
         <v>2</v>
       </c>
@@ -35054,7 +35045,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="34">
         <v>3</v>
       </c>
@@ -35110,7 +35101,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="34">
         <v>4</v>
       </c>
@@ -35166,7 +35157,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="34">
         <v>5</v>
       </c>
@@ -35222,7 +35213,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="40">
         <v>6</v>
       </c>
@@ -35274,11 +35265,11 @@
       <c r="Q7" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R7" s="241" t="s">
+      <c r="R7" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="40">
         <v>7</v>
       </c>
@@ -35330,11 +35321,11 @@
       <c r="Q8" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R8" s="241" t="s">
+      <c r="R8" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="40">
         <v>8</v>
       </c>
@@ -35386,11 +35377,11 @@
       <c r="Q9" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R9" s="241" t="s">
+      <c r="R9" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="40">
         <v>9</v>
       </c>
@@ -35442,11 +35433,11 @@
       <c r="Q10" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R10" s="241" t="s">
+      <c r="R10" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="40">
         <v>10</v>
       </c>
@@ -35498,11 +35489,11 @@
       <c r="Q11" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R11" s="241" t="s">
+      <c r="R11" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="40">
         <v>11</v>
       </c>
@@ -35554,11 +35545,11 @@
       <c r="Q12" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R12" s="241" t="s">
+      <c r="R12" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="40">
         <v>12</v>
       </c>
@@ -35610,11 +35601,11 @@
       <c r="Q13" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R13" s="241" t="s">
+      <c r="R13" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="40">
         <v>13</v>
       </c>
@@ -35666,11 +35657,11 @@
       <c r="Q14" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R14" s="241" t="s">
+      <c r="R14" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="40">
         <v>14</v>
       </c>
@@ -35722,11 +35713,11 @@
       <c r="Q15" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R15" s="241" t="s">
+      <c r="R15" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="40">
         <v>15</v>
       </c>
@@ -35778,11 +35769,11 @@
       <c r="Q16" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R16" s="241" t="s">
+      <c r="R16" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="40">
         <v>16</v>
       </c>
@@ -35834,11 +35825,11 @@
       <c r="Q17" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R17" s="241" t="s">
+      <c r="R17" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="40">
         <v>17</v>
       </c>
@@ -35890,11 +35881,11 @@
       <c r="Q18" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R18" s="241" t="s">
+      <c r="R18" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="40">
         <v>18</v>
       </c>
@@ -35947,11 +35938,11 @@
       <c r="Q19" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R19" s="241" t="s">
+      <c r="R19" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="40">
         <v>19</v>
       </c>
@@ -36003,11 +35994,11 @@
       <c r="Q20" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R20" s="241" t="s">
+      <c r="R20" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="40">
         <v>20</v>
       </c>
@@ -36059,11 +36050,11 @@
       <c r="Q21" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R21" s="241" t="s">
+      <c r="R21" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="40">
         <v>21</v>
       </c>
@@ -36115,11 +36106,11 @@
       <c r="Q22" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R22" s="241" t="s">
+      <c r="R22" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="40">
         <v>22</v>
       </c>
@@ -36171,11 +36162,11 @@
       <c r="Q23" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R23" s="241" t="s">
+      <c r="R23" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="40">
         <v>23</v>
       </c>
@@ -36227,11 +36218,11 @@
       <c r="Q24" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R24" s="241" t="s">
+      <c r="R24" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="40">
         <v>24</v>
       </c>
@@ -36283,11 +36274,11 @@
       <c r="Q25" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R25" s="241" t="s">
+      <c r="R25" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="40">
         <v>25</v>
       </c>
@@ -36339,11 +36330,11 @@
       <c r="Q26" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R26" s="241" t="s">
+      <c r="R26" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="40">
         <v>26</v>
       </c>
@@ -36395,11 +36386,11 @@
       <c r="Q27" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R27" s="241" t="s">
+      <c r="R27" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="40">
         <v>27</v>
       </c>
@@ -36451,11 +36442,11 @@
       <c r="Q28" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R28" s="241" t="s">
+      <c r="R28" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="40">
         <v>28</v>
       </c>
@@ -36507,11 +36498,11 @@
       <c r="Q29" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R29" s="241" t="s">
+      <c r="R29" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="40">
         <v>29</v>
       </c>
@@ -36563,11 +36554,11 @@
       <c r="Q30" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R30" s="241" t="s">
+      <c r="R30" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="40">
         <v>30</v>
       </c>
@@ -36619,11 +36610,11 @@
       <c r="Q31" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R31" s="241" t="s">
+      <c r="R31" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="40">
         <v>31</v>
       </c>
@@ -36675,11 +36666,11 @@
       <c r="Q32" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R32" s="241" t="s">
+      <c r="R32" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="40">
         <v>32</v>
       </c>
@@ -36731,11 +36722,11 @@
       <c r="Q33" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R33" s="241" t="s">
+      <c r="R33" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="40">
         <v>33</v>
       </c>
@@ -36787,11 +36778,11 @@
       <c r="Q34" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R34" s="241" t="s">
+      <c r="R34" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="40">
         <v>34</v>
       </c>
@@ -36843,11 +36834,11 @@
       <c r="Q35" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R35" s="241" t="s">
+      <c r="R35" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="40">
         <v>35</v>
       </c>
@@ -36899,11 +36890,11 @@
       <c r="Q36" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R36" s="241" t="s">
+      <c r="R36" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="40">
         <v>36</v>
       </c>
@@ -36955,11 +36946,11 @@
       <c r="Q37" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R37" s="241" t="s">
+      <c r="R37" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="40">
         <v>37</v>
       </c>
@@ -37011,11 +37002,11 @@
       <c r="Q38" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R38" s="241" t="s">
+      <c r="R38" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="40">
         <v>38</v>
       </c>
@@ -37067,11 +37058,11 @@
       <c r="Q39" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R39" s="241" t="s">
+      <c r="R39" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="40">
         <v>39</v>
       </c>
@@ -37123,11 +37114,11 @@
       <c r="Q40" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R40" s="241" t="s">
+      <c r="R40" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="40">
         <v>40</v>
       </c>
@@ -37179,11 +37170,11 @@
       <c r="Q41" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R41" s="241" t="s">
+      <c r="R41" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="40">
         <v>41</v>
       </c>
@@ -37235,11 +37226,11 @@
       <c r="Q42" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R42" s="241" t="s">
+      <c r="R42" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="40">
         <v>42</v>
       </c>
@@ -37291,11 +37282,11 @@
       <c r="Q43" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R43" s="241" t="s">
+      <c r="R43" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="40">
         <v>43</v>
       </c>
@@ -37347,11 +37338,11 @@
       <c r="Q44" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R44" s="241" t="s">
+      <c r="R44" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="40">
         <v>44</v>
       </c>
@@ -37403,11 +37394,11 @@
       <c r="Q45" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R45" s="241" t="s">
+      <c r="R45" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="40">
         <v>45</v>
       </c>
@@ -37459,11 +37450,11 @@
       <c r="Q46" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R46" s="241" t="s">
+      <c r="R46" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="40">
         <v>46</v>
       </c>
@@ -37515,11 +37506,11 @@
       <c r="Q47" s="220" t="s">
         <v>718</v>
       </c>
-      <c r="R47" s="241" t="s">
+      <c r="R47" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="59">
         <v>47</v>
       </c>
@@ -37575,7 +37566,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="190">
         <v>48</v>
       </c>
@@ -37621,7 +37612,7 @@
       <c r="O49" s="125">
         <v>0</v>
       </c>
-      <c r="P49" s="258" t="s">
+      <c r="P49" s="255" t="s">
         <v>751</v>
       </c>
       <c r="Q49" s="176" t="s">
@@ -37640,68 +37631,68 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:R33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="4.69921875" style="8" customWidth="1"/>
+    <col min="1" max="1" width="4.59765625" style="8" customWidth="1"/>
     <col min="2" max="2" width="53.796875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="14.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.796875" style="8" customWidth="1"/>
     <col min="5" max="5" width="17.59765625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="16.69921875" style="8" customWidth="1"/>
+    <col min="6" max="6" width="16.59765625" style="8" customWidth="1"/>
     <col min="7" max="7" width="14" style="13" customWidth="1"/>
-    <col min="8" max="8" width="15.09765625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="15" style="8" customWidth="1"/>
     <col min="9" max="9" width="16" style="9" customWidth="1"/>
     <col min="10" max="10" width="12.796875" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.8984375" style="8" customWidth="1"/>
+    <col min="11" max="11" width="25.796875" style="8" customWidth="1"/>
     <col min="12" max="12" width="12.3984375" style="8" customWidth="1"/>
     <col min="13" max="13" width="16.19921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.296875" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.59765625" style="9" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="71.19921875" style="9" customWidth="1"/>
     <col min="17" max="17" width="39.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="40.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="40.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="8.796875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="234" t="s">
         <v>520</v>
       </c>
-      <c r="B1" s="238" t="s">
+      <c r="B1" s="235" t="s">
         <v>705</v>
       </c>
-      <c r="C1" s="238" t="s">
+      <c r="C1" s="235" t="s">
         <v>706</v>
       </c>
       <c r="D1" s="235" t="s">
         <v>707</v>
       </c>
-      <c r="E1" s="239" t="s">
+      <c r="E1" s="234" t="s">
         <v>521</v>
       </c>
-      <c r="F1" s="239" t="s">
+      <c r="F1" s="234" t="s">
         <v>522</v>
       </c>
-      <c r="G1" s="239" t="s">
+      <c r="G1" s="234" t="s">
         <v>523</v>
       </c>
-      <c r="H1" s="239" t="s">
+      <c r="H1" s="234" t="s">
         <v>524</v>
       </c>
-      <c r="I1" s="239" t="s">
+      <c r="I1" s="234" t="s">
         <v>525</v>
       </c>
-      <c r="J1" s="240" t="s">
+      <c r="J1" s="236" t="s">
         <v>708</v>
       </c>
-      <c r="K1" s="240" t="s">
+      <c r="K1" s="236" t="s">
         <v>709</v>
       </c>
       <c r="L1" s="236" t="s">
         <v>710</v>
       </c>
       <c r="M1" s="237" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="N1" s="235" t="s">
         <v>713</v>
@@ -37719,7 +37710,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="26">
         <v>1</v>
       </c>
@@ -37775,7 +37766,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="34">
         <v>2</v>
       </c>
@@ -37831,7 +37822,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="34">
         <v>3</v>
       </c>
@@ -37887,7 +37878,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="34">
         <v>4</v>
       </c>
@@ -37943,7 +37934,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="40">
         <v>5</v>
       </c>
@@ -37999,7 +37990,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="40">
         <v>6</v>
       </c>
@@ -38055,7 +38046,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="40">
         <v>7</v>
       </c>
@@ -38111,7 +38102,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="40">
         <v>8</v>
       </c>
@@ -38167,7 +38158,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="40">
         <v>9</v>
       </c>
@@ -38223,7 +38214,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="40">
         <v>10</v>
       </c>
@@ -38279,7 +38270,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="47">
         <v>11</v>
       </c>
@@ -38335,7 +38326,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="47">
         <v>12</v>
       </c>
@@ -38391,7 +38382,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="47">
         <v>13</v>
       </c>
@@ -38447,7 +38438,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="47">
         <v>14</v>
       </c>
@@ -38503,7 +38494,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="47">
         <v>15</v>
       </c>
@@ -38559,7 +38550,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="47">
         <v>16</v>
       </c>
@@ -38615,7 +38606,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="47">
         <v>17</v>
       </c>
@@ -38671,7 +38662,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="47">
         <v>18</v>
       </c>
@@ -38727,7 +38718,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="47">
         <v>19</v>
       </c>
@@ -38783,7 +38774,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="52">
         <v>20</v>
       </c>
@@ -38839,7 +38830,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="190">
         <v>21</v>
       </c>
@@ -38885,7 +38876,7 @@
       <c r="O22" s="125">
         <v>0</v>
       </c>
-      <c r="P22" s="258" t="s">
+      <c r="P22" s="255" t="s">
         <v>719</v>
       </c>
       <c r="Q22" s="176" t="s">
@@ -38895,21 +38886,21 @@
         <v>519</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="24" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="8" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:18" ht="17.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="26" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="27" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="28" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="29" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="30" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="31" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="33" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <autoFilter ref="A1:R22" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -38919,30 +38910,30 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:R37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="4.69921875" style="8" customWidth="1"/>
+    <col min="1" max="1" width="4.59765625" style="8" customWidth="1"/>
     <col min="2" max="2" width="53.796875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="13.296875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="13.19921875" style="8" customWidth="1"/>
     <col min="4" max="4" width="17.796875" style="8" customWidth="1"/>
     <col min="5" max="5" width="17.59765625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="16.69921875" style="8" customWidth="1"/>
+    <col min="6" max="6" width="16.59765625" style="8" customWidth="1"/>
     <col min="7" max="7" width="14" style="8" customWidth="1"/>
-    <col min="8" max="8" width="15.09765625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="15" style="8" customWidth="1"/>
     <col min="9" max="9" width="16" style="8" customWidth="1"/>
-    <col min="10" max="10" width="12.8984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.69921875" style="8" customWidth="1"/>
-    <col min="13" max="13" width="11.69921875" style="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.59765625" style="8" customWidth="1"/>
+    <col min="13" max="13" width="11.59765625" style="16" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="67.69921875" style="8" customWidth="1"/>
+    <col min="15" max="15" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="67.59765625" style="8" customWidth="1"/>
     <col min="17" max="17" width="39.19921875" style="8" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="41.19921875" style="8" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="8.796875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="9" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="9" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="234" t="s">
         <v>520</v>
       </c>
@@ -38998,7 +38989,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="12" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="12" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="82">
         <v>1</v>
       </c>
@@ -39054,7 +39045,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="79">
         <v>2</v>
       </c>
@@ -39110,7 +39101,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="75">
         <v>3</v>
       </c>
@@ -39166,7 +39157,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="75">
         <v>4</v>
       </c>
@@ -39222,7 +39213,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="75">
         <v>5</v>
       </c>
@@ -39278,7 +39269,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="69">
         <v>6</v>
       </c>
@@ -39327,14 +39318,14 @@
       <c r="P7" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q7" s="241" t="s">
+      <c r="Q7" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R7" s="241" t="s">
+      <c r="R7" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="69">
         <v>7</v>
       </c>
@@ -39383,14 +39374,14 @@
       <c r="P8" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q8" s="241" t="s">
+      <c r="Q8" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R8" s="241" t="s">
+      <c r="R8" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="69">
         <v>8</v>
       </c>
@@ -39439,14 +39430,14 @@
       <c r="P9" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q9" s="241" t="s">
+      <c r="Q9" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R9" s="241" t="s">
+      <c r="R9" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="69">
         <v>9</v>
       </c>
@@ -39495,14 +39486,14 @@
       <c r="P10" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q10" s="241" t="s">
+      <c r="Q10" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R10" s="241" t="s">
+      <c r="R10" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="69">
         <v>10</v>
       </c>
@@ -39551,14 +39542,14 @@
       <c r="P11" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q11" s="241" t="s">
+      <c r="Q11" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R11" s="241" t="s">
+      <c r="R11" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="69">
         <v>11</v>
       </c>
@@ -39607,14 +39598,14 @@
       <c r="P12" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q12" s="241" t="s">
+      <c r="Q12" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R12" s="241" t="s">
+      <c r="R12" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="69">
         <v>12</v>
       </c>
@@ -39663,14 +39654,14 @@
       <c r="P13" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q13" s="241" t="s">
+      <c r="Q13" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R13" s="241" t="s">
+      <c r="R13" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="69">
         <v>13</v>
       </c>
@@ -39719,14 +39710,14 @@
       <c r="P14" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q14" s="241" t="s">
+      <c r="Q14" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R14" s="241" t="s">
+      <c r="R14" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="69">
         <v>14</v>
       </c>
@@ -39775,14 +39766,14 @@
       <c r="P15" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q15" s="241" t="s">
+      <c r="Q15" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R15" s="241" t="s">
+      <c r="R15" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="69">
         <v>15</v>
       </c>
@@ -39831,14 +39822,14 @@
       <c r="P16" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q16" s="241" t="s">
+      <c r="Q16" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R16" s="241" t="s">
+      <c r="R16" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="69">
         <v>16</v>
       </c>
@@ -39887,14 +39878,14 @@
       <c r="P17" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q17" s="241" t="s">
+      <c r="Q17" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R17" s="241" t="s">
+      <c r="R17" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="69">
         <v>17</v>
       </c>
@@ -39943,14 +39934,14 @@
       <c r="P18" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q18" s="241" t="s">
+      <c r="Q18" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R18" s="241" t="s">
+      <c r="R18" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="69">
         <v>18</v>
       </c>
@@ -39999,14 +39990,14 @@
       <c r="P19" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q19" s="241" t="s">
+      <c r="Q19" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R19" s="241" t="s">
+      <c r="R19" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="69">
         <v>19</v>
       </c>
@@ -40055,14 +40046,14 @@
       <c r="P20" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q20" s="241" t="s">
+      <c r="Q20" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R20" s="241" t="s">
+      <c r="R20" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="69">
         <v>20</v>
       </c>
@@ -40111,14 +40102,14 @@
       <c r="P21" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q21" s="241" t="s">
+      <c r="Q21" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R21" s="241" t="s">
+      <c r="R21" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="69">
         <v>21</v>
       </c>
@@ -40167,14 +40158,14 @@
       <c r="P22" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q22" s="241" t="s">
+      <c r="Q22" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R22" s="241" t="s">
+      <c r="R22" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="69">
         <v>22</v>
       </c>
@@ -40223,14 +40214,14 @@
       <c r="P23" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q23" s="241" t="s">
+      <c r="Q23" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R23" s="241" t="s">
+      <c r="R23" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="69">
         <v>23</v>
       </c>
@@ -40279,14 +40270,14 @@
       <c r="P24" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q24" s="241" t="s">
+      <c r="Q24" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R24" s="241" t="s">
+      <c r="R24" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="69">
         <v>24</v>
       </c>
@@ -40335,14 +40326,14 @@
       <c r="P25" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q25" s="241" t="s">
+      <c r="Q25" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R25" s="241" t="s">
+      <c r="R25" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="69">
         <v>25</v>
       </c>
@@ -40391,14 +40382,14 @@
       <c r="P26" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q26" s="241" t="s">
+      <c r="Q26" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R26" s="241" t="s">
+      <c r="R26" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="69">
         <v>26</v>
       </c>
@@ -40447,14 +40438,14 @@
       <c r="P27" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q27" s="241" t="s">
+      <c r="Q27" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R27" s="241" t="s">
+      <c r="R27" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="69">
         <v>27</v>
       </c>
@@ -40503,14 +40494,14 @@
       <c r="P28" s="225" t="s">
         <v>1376</v>
       </c>
-      <c r="Q28" s="241" t="s">
+      <c r="Q28" s="238" t="s">
         <v>718</v>
       </c>
-      <c r="R28" s="241" t="s">
+      <c r="R28" s="238" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="65">
         <v>28</v>
       </c>
@@ -40566,7 +40557,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="65">
         <v>29</v>
       </c>
@@ -40622,7 +40613,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="65">
         <v>30</v>
       </c>
@@ -40678,25 +40669,25 @@
         <v>574</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="34" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="35" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="303"/>
-      <c r="B36" s="303"/>
-      <c r="C36" s="303"/>
-      <c r="D36" s="303"/>
-      <c r="E36" s="303"/>
-      <c r="F36" s="303"/>
-      <c r="G36" s="303"/>
-      <c r="H36" s="303"/>
-      <c r="I36" s="303"/>
-      <c r="J36" s="303"/>
-      <c r="K36" s="303"/>
-      <c r="L36" s="303"/>
-    </row>
-    <row r="37" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="33" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="34" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="35" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="36" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="300"/>
+      <c r="B36" s="300"/>
+      <c r="C36" s="300"/>
+      <c r="D36" s="300"/>
+      <c r="E36" s="300"/>
+      <c r="F36" s="300"/>
+      <c r="G36" s="300"/>
+      <c r="H36" s="300"/>
+      <c r="I36" s="300"/>
+      <c r="J36" s="300"/>
+      <c r="K36" s="300"/>
+      <c r="L36" s="300"/>
+    </row>
+    <row r="37" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <autoFilter ref="A1:R31" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
   <mergeCells count="1">
@@ -40709,29 +40700,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:R27"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="4.69921875" style="19" customWidth="1"/>
+    <col min="1" max="1" width="4.59765625" style="19" customWidth="1"/>
     <col min="2" max="2" width="36" style="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.59765625" style="19" customWidth="1"/>
     <col min="4" max="4" width="14.59765625" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.19921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.3984375" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13" style="19" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.8984375" style="21" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.09765625" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.69921875" style="19" customWidth="1"/>
+    <col min="10" max="10" width="13.796875" style="21" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.59765625" style="19" customWidth="1"/>
     <col min="13" max="13" width="11.796875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="58.09765625" customWidth="1"/>
-    <col min="17" max="17" width="38.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="39.8984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="58" customWidth="1"/>
+    <col min="17" max="17" width="38.3984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="39.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="7" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" s="7" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="234" t="s">
         <v>520</v>
       </c>
@@ -40768,7 +40759,7 @@
       <c r="L1" s="237" t="s">
         <v>710</v>
       </c>
-      <c r="M1" s="259" t="s">
+      <c r="M1" s="256" t="s">
         <v>712</v>
       </c>
       <c r="N1" s="235" t="s">
@@ -40787,7 +40778,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="130">
         <v>1</v>
       </c>
@@ -40843,7 +40834,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="40">
         <v>2</v>
       </c>
@@ -40899,7 +40890,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="40">
         <v>3</v>
       </c>
@@ -40955,7 +40946,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="40">
         <v>4</v>
       </c>
@@ -41011,7 +41002,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="40">
         <v>5</v>
       </c>
@@ -41067,7 +41058,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="40">
         <v>6</v>
       </c>
@@ -41123,7 +41114,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="40">
         <v>7</v>
       </c>
@@ -41172,32 +41163,32 @@
       <c r="P8" s="225" t="s">
         <v>1386</v>
       </c>
-      <c r="Q8" s="260" t="s">
+      <c r="Q8" s="257" t="s">
         <v>718</v>
       </c>
-      <c r="R8" s="260" t="s">
+      <c r="R8" s="257" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:18" ht="17.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" ht="17.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="10" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="11" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="13" spans="1:18" ht="17.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="14" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="15" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="16" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="17" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="19" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="20" ht="17.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="22" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="23" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="24" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="25" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="26" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="27" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <autoFilter ref="A1:R8" xr:uid="{00000000-0001-0000-0600-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -41207,28 +41198,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:R49"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.19921875" customWidth="1"/>
-    <col min="2" max="2" width="43.09765625" customWidth="1"/>
-    <col min="3" max="3" width="14.09765625" customWidth="1"/>
-    <col min="4" max="4" width="17.09765625" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="6" width="21.59765625" customWidth="1"/>
-    <col min="7" max="7" width="13.296875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="13.19921875" style="5" customWidth="1"/>
     <col min="8" max="8" width="14.3984375" style="4" customWidth="1"/>
     <col min="9" max="9" width="16" style="7" customWidth="1"/>
-    <col min="10" max="10" width="13.8984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.796875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="25.796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.8984375" customWidth="1"/>
-    <col min="13" max="13" width="11.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.796875" customWidth="1"/>
+    <col min="13" max="13" width="11.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.796875" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="64.3984375" customWidth="1"/>
-    <col min="17" max="17" width="42.296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="42.19921875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="39.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="234" t="s">
         <v>520</v>
       </c>
@@ -41284,7 +41275,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="95">
         <v>1</v>
       </c>
@@ -41333,14 +41324,14 @@
       <c r="P2" s="102" t="s">
         <v>1379</v>
       </c>
-      <c r="Q2" s="242" t="s">
+      <c r="Q2" s="239" t="s">
         <v>1372</v>
       </c>
-      <c r="R2" s="242" t="s">
+      <c r="R2" s="239" t="s">
         <v>1404</v>
       </c>
     </row>
-    <row r="3" spans="1:18" s="14" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="14" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="104">
         <v>2</v>
       </c>
@@ -41396,7 +41387,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="14" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="14" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="104">
         <v>3</v>
       </c>
@@ -41452,7 +41443,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="14" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="14" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="104">
         <v>4</v>
       </c>
@@ -41508,7 +41499,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="14" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="14" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="104">
         <v>5</v>
       </c>
@@ -41564,7 +41555,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="14" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="14" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="104">
         <v>6</v>
       </c>
@@ -41620,7 +41611,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="14" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="14" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="104">
         <v>7</v>
       </c>
@@ -41676,7 +41667,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="14" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="14" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="104">
         <v>8</v>
       </c>
@@ -41732,7 +41723,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="14" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="14" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="104">
         <v>9</v>
       </c>
@@ -41788,7 +41779,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="14" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="14" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="104">
         <v>10</v>
       </c>
@@ -41844,7 +41835,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="47">
         <v>11</v>
       </c>
@@ -41900,7 +41891,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="47">
         <v>12</v>
       </c>
@@ -41956,7 +41947,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="47">
         <v>13</v>
       </c>
@@ -42012,7 +42003,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="47">
         <v>14</v>
       </c>
@@ -42068,7 +42059,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="47">
         <v>15</v>
       </c>
@@ -42124,7 +42115,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="47">
         <v>16</v>
       </c>
@@ -42180,7 +42171,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="47">
         <v>17</v>
       </c>
@@ -42236,7 +42227,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="47">
         <v>18</v>
       </c>
@@ -42292,7 +42283,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="47">
         <v>19</v>
       </c>
@@ -42348,7 +42339,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="47">
         <v>20</v>
       </c>
@@ -42404,7 +42395,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="47">
         <v>21</v>
       </c>
@@ -42460,7 +42451,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="47">
         <v>22</v>
       </c>
@@ -42516,7 +42507,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="47">
         <v>23</v>
       </c>
@@ -42572,7 +42563,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="47">
         <v>24</v>
       </c>
@@ -42628,7 +42619,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="47">
         <v>25</v>
       </c>
@@ -42684,7 +42675,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="47">
         <v>26</v>
       </c>
@@ -42740,7 +42731,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="47">
         <v>27</v>
       </c>
@@ -42796,7 +42787,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="47">
         <v>28</v>
       </c>
@@ -42852,7 +42843,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="47">
         <v>29</v>
       </c>
@@ -42908,7 +42899,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="47">
         <v>30</v>
       </c>
@@ -42964,7 +42955,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="47">
         <v>31</v>
       </c>
@@ -43020,7 +43011,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="47">
         <v>32</v>
       </c>
@@ -43076,7 +43067,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="47">
         <v>33</v>
       </c>
@@ -43132,7 +43123,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="47">
         <v>34</v>
       </c>
@@ -43188,7 +43179,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="47">
         <v>35</v>
       </c>
@@ -43244,7 +43235,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="47">
         <v>36</v>
       </c>
@@ -43300,7 +43291,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="47">
         <v>37</v>
       </c>
@@ -43356,7 +43347,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="47">
         <v>38</v>
       </c>
@@ -43412,7 +43403,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="111">
         <v>39</v>
       </c>
@@ -43468,7 +43459,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="111">
         <v>40</v>
       </c>
@@ -43524,7 +43515,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="111">
         <v>41</v>
       </c>
@@ -43580,7 +43571,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="52">
         <v>42</v>
       </c>
@@ -43636,7 +43627,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="118">
         <v>43</v>
       </c>
@@ -43692,7 +43683,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="118">
         <v>44</v>
       </c>
@@ -43748,7 +43739,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="120">
         <v>45</v>
       </c>
@@ -43794,7 +43785,7 @@
       <c r="O46" s="125">
         <v>0</v>
       </c>
-      <c r="P46" s="250" t="s">
+      <c r="P46" s="247" t="s">
         <v>719</v>
       </c>
       <c r="Q46" s="223" t="s">
@@ -43804,7 +43795,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="120">
         <v>46</v>
       </c>
@@ -43850,7 +43841,7 @@
       <c r="O47" s="125">
         <v>0</v>
       </c>
-      <c r="P47" s="250" t="s">
+      <c r="P47" s="247" t="s">
         <v>719</v>
       </c>
       <c r="Q47" s="223" t="s">
@@ -43860,7 +43851,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="120">
         <v>47</v>
       </c>
@@ -43906,7 +43897,7 @@
       <c r="O48" s="125">
         <v>0</v>
       </c>
-      <c r="P48" s="250" t="s">
+      <c r="P48" s="247" t="s">
         <v>719</v>
       </c>
       <c r="Q48" s="223" t="s">
@@ -43916,7 +43907,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="120">
         <v>48</v>
       </c>
@@ -43962,7 +43953,7 @@
       <c r="O49" s="125">
         <v>0</v>
       </c>
-      <c r="P49" s="255" t="s">
+      <c r="P49" s="252" t="s">
         <v>719</v>
       </c>
       <c r="Q49" s="200" t="s">
@@ -43981,28 +43972,28 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.19921875" customWidth="1"/>
-    <col min="2" max="2" width="39.296875" customWidth="1"/>
+    <col min="2" max="2" width="39.19921875" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="24.19921875" customWidth="1"/>
     <col min="5" max="6" width="21.59765625" customWidth="1"/>
-    <col min="7" max="7" width="13.296875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="13.19921875" style="5" customWidth="1"/>
     <col min="8" max="8" width="14.3984375" style="5" customWidth="1"/>
     <col min="9" max="9" width="16" style="7" customWidth="1"/>
     <col min="10" max="10" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="28.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.59765625" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="24.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="55.5" customWidth="1"/>
+    <col min="15" max="15" width="15.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="55.3984375" customWidth="1"/>
     <col min="17" max="17" width="38.3984375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="39.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="22" t="s">
         <v>520</v>
       </c>
@@ -44058,7 +44049,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="126">
         <v>1</v>
       </c>
@@ -44114,7 +44105,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="130">
         <v>2</v>
       </c>
@@ -44170,7 +44161,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="130">
         <v>3</v>
       </c>
@@ -44226,7 +44217,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="130">
         <v>4</v>
       </c>
@@ -44282,7 +44273,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="130">
         <v>5</v>
       </c>
@@ -44338,7 +44329,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="130">
         <v>6</v>
       </c>
@@ -44394,7 +44385,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="130">
         <v>7</v>
       </c>
@@ -44450,7 +44441,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="130">
         <v>8</v>
       </c>
@@ -44506,7 +44497,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="47">
         <v>9</v>
       </c>
@@ -44562,7 +44553,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="47">
         <v>10</v>
       </c>
@@ -44618,7 +44609,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="47">
         <v>11</v>
       </c>
@@ -44674,7 +44665,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="47">
         <v>12</v>
       </c>
@@ -44730,7 +44721,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="47">
         <v>13</v>
       </c>
@@ -44786,7 +44777,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="47">
         <v>14</v>
       </c>
@@ -44842,7 +44833,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="47">
         <v>15</v>
       </c>
@@ -44898,7 +44889,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="47">
         <v>16</v>
       </c>
@@ -44954,7 +44945,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="47">
         <v>17</v>
       </c>
@@ -45010,7 +45001,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="47">
         <v>18</v>
       </c>
@@ -45066,7 +45057,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="47">
         <v>19</v>
       </c>
@@ -45122,7 +45113,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="47">
         <v>20</v>
       </c>
@@ -45176,7 +45167,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="47">
         <v>21</v>
       </c>
@@ -45232,7 +45223,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="47">
         <v>22</v>
       </c>
@@ -45288,7 +45279,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="47">
         <v>23</v>
       </c>
@@ -45344,7 +45335,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="47">
         <v>24</v>
       </c>
@@ -45400,7 +45391,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="47">
         <v>25</v>
       </c>
@@ -45456,7 +45447,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="47">
         <v>26</v>
       </c>
@@ -45512,7 +45503,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="47">
         <v>27</v>
       </c>
@@ -45568,7 +45559,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="47">
         <v>28</v>
       </c>
@@ -45624,7 +45615,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="47">
         <v>29</v>
       </c>
@@ -45680,7 +45671,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="47">
         <v>30</v>
       </c>
@@ -45736,7 +45727,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="47">
         <v>31</v>
       </c>
@@ -45792,7 +45783,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="47">
         <v>32</v>
       </c>
@@ -45848,7 +45839,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="47">
         <v>33</v>
       </c>
@@ -45904,7 +45895,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="47">
         <v>34</v>
       </c>
@@ -45960,7 +45951,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="47">
         <v>35</v>
       </c>
@@ -46016,7 +46007,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="47">
         <v>36</v>
       </c>
@@ -46072,7 +46063,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="47">
         <v>37</v>
       </c>
@@ -46128,7 +46119,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="47">
         <v>38</v>
       </c>
@@ -46184,7 +46175,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="111">
         <v>39</v>
       </c>
@@ -46240,7 +46231,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="118">
         <v>40</v>
       </c>
@@ -46286,7 +46277,7 @@
       <c r="O41" s="56">
         <v>3</v>
       </c>
-      <c r="P41" s="244" t="s">
+      <c r="P41" s="241" t="s">
         <v>738</v>
       </c>
       <c r="Q41" s="66" t="s">
@@ -46296,7 +46287,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="118">
         <v>41</v>
       </c>
@@ -46342,7 +46333,7 @@
       <c r="O42" s="56">
         <v>0</v>
       </c>
-      <c r="P42" s="244" t="s">
+      <c r="P42" s="241" t="s">
         <v>739</v>
       </c>
       <c r="Q42" s="66" t="s">
@@ -46352,7 +46343,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="52">
         <v>42</v>
       </c>
@@ -46398,17 +46389,17 @@
       <c r="O43" s="56">
         <v>6</v>
       </c>
-      <c r="P43" s="245" t="s">
+      <c r="P43" s="242" t="s">
         <v>1395</v>
       </c>
-      <c r="Q43" s="247" t="s">
+      <c r="Q43" s="244" t="s">
         <v>718</v>
       </c>
-      <c r="R43" s="247" t="s">
+      <c r="R43" s="244" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="52">
         <v>43</v>
       </c>
@@ -46457,10 +46448,10 @@
       <c r="P44" s="219" t="s">
         <v>1392</v>
       </c>
-      <c r="Q44" s="248" t="s">
+      <c r="Q44" s="245" t="s">
         <v>718</v>
       </c>
-      <c r="R44" s="248" t="s">
+      <c r="R44" s="245" t="s">
         <v>516</v>
       </c>
     </row>
@@ -46474,28 +46465,28 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:R36"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.19921875" style="19" customWidth="1"/>
-    <col min="2" max="2" width="39.296875" customWidth="1"/>
-    <col min="3" max="3" width="21.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.19921875" customWidth="1"/>
+    <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.19921875" customWidth="1"/>
     <col min="5" max="6" width="21.59765625" customWidth="1"/>
-    <col min="7" max="7" width="13.296875" customWidth="1"/>
+    <col min="7" max="7" width="13.19921875" customWidth="1"/>
     <col min="8" max="8" width="14.3984375" customWidth="1"/>
     <col min="9" max="9" width="16" style="7" customWidth="1"/>
-    <col min="10" max="10" width="13.8984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.8984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.796875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.8984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.796875" style="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="26.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="53.8984375" customWidth="1"/>
-    <col min="17" max="17" width="39.8984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="41.296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="53.796875" customWidth="1"/>
+    <col min="17" max="17" width="39.796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="41.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="22" t="s">
         <v>520</v>
       </c>
@@ -46551,7 +46542,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="126">
         <v>1</v>
       </c>
@@ -46607,7 +46598,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="34">
         <v>2</v>
       </c>
@@ -46663,7 +46654,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="34">
         <v>3</v>
       </c>
@@ -46719,7 +46710,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="34">
         <v>4</v>
       </c>
@@ -46775,7 +46766,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="34">
         <v>5</v>
       </c>
@@ -46831,7 +46822,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="34">
         <v>6</v>
       </c>
@@ -46887,7 +46878,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="34">
         <v>7</v>
       </c>
@@ -46943,7 +46934,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="34">
         <v>8</v>
       </c>
@@ -46999,7 +46990,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="40">
         <v>9</v>
       </c>
@@ -47055,7 +47046,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="40">
         <v>10</v>
       </c>
@@ -47111,7 +47102,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="40">
         <v>11</v>
       </c>
@@ -47167,7 +47158,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="40">
         <v>12</v>
       </c>
@@ -47223,7 +47214,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="40">
         <v>13</v>
       </c>
@@ -47279,7 +47270,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="40">
         <v>14</v>
       </c>
@@ -47335,7 +47326,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="40">
         <v>15</v>
       </c>
@@ -47391,7 +47382,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="40">
         <v>16</v>
       </c>
@@ -47447,7 +47438,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="40">
         <v>17</v>
       </c>
@@ -47503,7 +47494,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="40">
         <v>18</v>
       </c>
@@ -47559,7 +47550,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="40">
         <v>19</v>
       </c>
@@ -47615,7 +47606,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="40">
         <v>20</v>
       </c>
@@ -47671,7 +47662,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="40">
         <v>21</v>
       </c>
@@ -47727,7 +47718,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="40">
         <v>22</v>
       </c>
@@ -47783,7 +47774,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="40">
         <v>23</v>
       </c>
@@ -47839,7 +47830,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="40">
         <v>24</v>
       </c>
@@ -47895,7 +47886,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="40">
         <v>25</v>
       </c>
@@ -47951,7 +47942,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="40">
         <v>26</v>
       </c>
@@ -48007,7 +47998,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="40">
         <v>27</v>
       </c>
@@ -48063,7 +48054,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="40">
         <v>28</v>
       </c>
@@ -48119,7 +48110,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="40">
         <v>29</v>
       </c>
@@ -48175,7 +48166,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="40">
         <v>30</v>
       </c>
@@ -48231,7 +48222,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="40">
         <v>31</v>
       </c>
@@ -48277,17 +48268,17 @@
       <c r="O32" s="72">
         <v>0</v>
       </c>
-      <c r="P32" s="249" t="s">
+      <c r="P32" s="246" t="s">
         <v>740</v>
       </c>
-      <c r="Q32" s="243" t="s">
+      <c r="Q32" s="240" t="s">
         <v>1403</v>
       </c>
       <c r="R32" s="220" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="40">
         <v>32</v>
       </c>
@@ -48333,17 +48324,17 @@
       <c r="O33" s="72">
         <v>0</v>
       </c>
-      <c r="P33" s="249" t="s">
+      <c r="P33" s="246" t="s">
         <v>740</v>
       </c>
-      <c r="Q33" s="243" t="s">
+      <c r="Q33" s="240" t="s">
         <v>1403</v>
       </c>
       <c r="R33" s="220" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="40">
         <v>33</v>
       </c>
@@ -48389,17 +48380,17 @@
       <c r="O34" s="72">
         <v>0</v>
       </c>
-      <c r="P34" s="249" t="s">
+      <c r="P34" s="246" t="s">
         <v>740</v>
       </c>
-      <c r="Q34" s="243" t="s">
+      <c r="Q34" s="240" t="s">
         <v>1403</v>
       </c>
       <c r="R34" s="220" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="52">
         <v>34</v>
       </c>
@@ -48455,7 +48446,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="52">
         <v>35</v>
       </c>
@@ -48520,7 +48511,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:R75"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.19921875" style="1" customWidth="1"/>
     <col min="2" max="2" width="47.59765625" style="21" bestFit="1" customWidth="1"/>
@@ -48528,12 +48519,12 @@
     <col min="4" max="4" width="24.19921875" style="21" customWidth="1"/>
     <col min="5" max="5" width="21.59765625" style="21" customWidth="1"/>
     <col min="6" max="6" width="21.59765625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="13.296875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="13.19921875" style="5" customWidth="1"/>
     <col min="8" max="8" width="14.3984375" style="4" customWidth="1"/>
     <col min="9" max="9" width="16" style="7" customWidth="1"/>
-    <col min="10" max="10" width="13.09765625" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
     <col min="11" max="11" width="37" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.3984375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" style="7" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19" style="7" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.19921875" style="7" bestFit="1" customWidth="1"/>
@@ -48542,7 +48533,7 @@
     <col min="18" max="18" width="39.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="22" t="s">
         <v>520</v>
       </c>
@@ -48598,7 +48589,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="153">
         <v>1</v>
       </c>
@@ -48647,14 +48638,14 @@
       <c r="P2" s="160" t="s">
         <v>1422</v>
       </c>
-      <c r="Q2" s="277" t="s">
+      <c r="Q2" s="274" t="s">
         <v>1397</v>
       </c>
       <c r="R2" s="160" t="s">
         <v>1404</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="38">
         <v>2</v>
       </c>
@@ -48710,7 +48701,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="38">
         <v>3</v>
       </c>
@@ -48766,7 +48757,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="38">
         <v>4</v>
       </c>
@@ -48822,7 +48813,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="38">
         <v>5</v>
       </c>
@@ -48878,7 +48869,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="38">
         <v>6</v>
       </c>
@@ -48934,7 +48925,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="45">
         <v>7</v>
       </c>
@@ -48990,7 +48981,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="45">
         <v>8</v>
       </c>
@@ -49046,7 +49037,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="45">
         <v>9</v>
       </c>
@@ -49102,7 +49093,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="45">
         <v>10</v>
       </c>
@@ -49158,7 +49149,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="45">
         <v>11</v>
       </c>
@@ -49214,7 +49205,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="45">
         <v>12</v>
       </c>
@@ -49270,7 +49261,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="45">
         <v>13</v>
       </c>
@@ -49326,7 +49317,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="45">
         <v>14</v>
       </c>
@@ -49382,7 +49373,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="45">
         <v>15</v>
       </c>
@@ -49438,7 +49429,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="45">
         <v>16</v>
       </c>
@@ -49494,7 +49485,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="45">
         <v>17</v>
       </c>
@@ -49550,7 +49541,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="45">
         <v>18</v>
       </c>
@@ -49606,7 +49597,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="45">
         <v>19</v>
       </c>
@@ -49662,7 +49653,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="63">
         <v>20</v>
       </c>
@@ -49709,10 +49700,10 @@
         <v>5</v>
       </c>
       <c r="P21" s="167"/>
-      <c r="Q21" s="278"/>
+      <c r="Q21" s="275"/>
       <c r="R21" s="168"/>
     </row>
-    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="63">
         <v>21</v>
       </c>
@@ -49758,7 +49749,7 @@
       <c r="Q22" s="64"/>
       <c r="R22" s="64"/>
     </row>
-    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="63">
         <v>22</v>
       </c>
@@ -49808,7 +49799,7 @@
       <c r="Q23" s="64"/>
       <c r="R23" s="64"/>
     </row>
-    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="63">
         <v>23</v>
       </c>
@@ -49858,7 +49849,7 @@
       <c r="Q24" s="64"/>
       <c r="R24" s="64"/>
     </row>
-    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="63">
         <v>24</v>
       </c>
@@ -49914,7 +49905,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="63">
         <v>25</v>
       </c>
@@ -49964,7 +49955,7 @@
       <c r="Q26" s="64"/>
       <c r="R26" s="135"/>
     </row>
-    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="63">
         <v>26</v>
       </c>
@@ -50014,7 +50005,7 @@
       <c r="Q27" s="64"/>
       <c r="R27" s="64"/>
     </row>
-    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="63">
         <v>27</v>
       </c>
@@ -50064,7 +50055,7 @@
       <c r="Q28" s="64"/>
       <c r="R28" s="64"/>
     </row>
-    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="63">
         <v>28</v>
       </c>
@@ -50114,7 +50105,7 @@
       <c r="Q29" s="64"/>
       <c r="R29" s="64"/>
     </row>
-    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="63">
         <v>29</v>
       </c>
@@ -50164,7 +50155,7 @@
       <c r="Q30" s="64"/>
       <c r="R30" s="64"/>
     </row>
-    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="63">
         <v>30</v>
       </c>
@@ -50214,7 +50205,7 @@
       <c r="Q31" s="64"/>
       <c r="R31" s="64"/>
     </row>
-    <row r="32" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="63">
         <v>31</v>
       </c>
@@ -50264,7 +50255,7 @@
       <c r="Q32" s="64"/>
       <c r="R32" s="64"/>
     </row>
-    <row r="33" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="63">
         <v>32</v>
       </c>
@@ -50314,7 +50305,7 @@
       <c r="Q33" s="64"/>
       <c r="R33" s="64"/>
     </row>
-    <row r="34" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="63">
         <v>33</v>
       </c>
@@ -50364,7 +50355,7 @@
       <c r="Q34" s="64"/>
       <c r="R34" s="64"/>
     </row>
-    <row r="35" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="63">
         <v>34</v>
       </c>
@@ -50414,7 +50405,7 @@
       <c r="Q35" s="64"/>
       <c r="R35" s="64"/>
     </row>
-    <row r="36" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="56">
         <v>35</v>
       </c>
@@ -50458,7 +50449,7 @@
       <c r="Q36" s="66"/>
       <c r="R36" s="66"/>
     </row>
-    <row r="37" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="56">
         <v>36</v>
       </c>
@@ -50502,7 +50493,7 @@
       <c r="Q37" s="66"/>
       <c r="R37" s="66"/>
     </row>
-    <row r="38" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="56">
         <v>37</v>
       </c>
@@ -50546,7 +50537,7 @@
       <c r="Q38" s="66"/>
       <c r="R38" s="66"/>
     </row>
-    <row r="39" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="56">
         <v>38</v>
       </c>
@@ -50590,7 +50581,7 @@
       <c r="Q39" s="66"/>
       <c r="R39" s="66"/>
     </row>
-    <row r="40" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="56">
         <v>39</v>
       </c>
@@ -50638,7 +50629,7 @@
       <c r="Q40" s="66"/>
       <c r="R40" s="66"/>
     </row>
-    <row r="41" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="56">
         <v>40</v>
       </c>
@@ -50688,7 +50679,7 @@
       <c r="Q41" s="66"/>
       <c r="R41" s="66"/>
     </row>
-    <row r="42" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="56">
         <v>41</v>
       </c>
@@ -50738,7 +50729,7 @@
       <c r="Q42" s="66"/>
       <c r="R42" s="66"/>
     </row>
-    <row r="43" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="56">
         <v>42</v>
       </c>
@@ -50788,7 +50779,7 @@
       <c r="Q43" s="66"/>
       <c r="R43" s="66"/>
     </row>
-    <row r="44" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="56">
         <v>43</v>
       </c>
@@ -50836,7 +50827,7 @@
       <c r="Q44" s="66"/>
       <c r="R44" s="66"/>
     </row>
-    <row r="45" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="56">
         <v>44</v>
       </c>
@@ -50886,7 +50877,7 @@
       <c r="Q45" s="66"/>
       <c r="R45" s="66"/>
     </row>
-    <row r="46" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="56">
         <v>45</v>
       </c>
@@ -50936,7 +50927,7 @@
       <c r="Q46" s="66"/>
       <c r="R46" s="66"/>
     </row>
-    <row r="47" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="56">
         <v>46</v>
       </c>
@@ -50986,7 +50977,7 @@
       <c r="Q47" s="66"/>
       <c r="R47" s="66"/>
     </row>
-    <row r="48" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="56">
         <v>47</v>
       </c>
@@ -51036,7 +51027,7 @@
       <c r="Q48" s="66"/>
       <c r="R48" s="66"/>
     </row>
-    <row r="49" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="56">
         <v>48</v>
       </c>
@@ -51086,7 +51077,7 @@
       <c r="Q49" s="66"/>
       <c r="R49" s="66"/>
     </row>
-    <row r="50" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="56">
         <v>49</v>
       </c>
@@ -51136,7 +51127,7 @@
       <c r="Q50" s="66"/>
       <c r="R50" s="66"/>
     </row>
-    <row r="51" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="56">
         <v>50</v>
       </c>
@@ -51186,7 +51177,7 @@
       <c r="Q51" s="66"/>
       <c r="R51" s="66"/>
     </row>
-    <row r="52" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="125">
         <v>51</v>
       </c>
@@ -51232,17 +51223,17 @@
       <c r="O52" s="175">
         <v>0</v>
       </c>
-      <c r="P52" s="250" t="s">
+      <c r="P52" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q52" s="279" t="s">
+      <c r="Q52" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R52" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="125">
         <v>52</v>
       </c>
@@ -51288,17 +51279,17 @@
       <c r="O53" s="175">
         <v>0</v>
       </c>
-      <c r="P53" s="250" t="s">
+      <c r="P53" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q53" s="279" t="s">
+      <c r="Q53" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R53" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="125">
         <v>53</v>
       </c>
@@ -51344,17 +51335,17 @@
       <c r="O54" s="175">
         <v>0</v>
       </c>
-      <c r="P54" s="250" t="s">
+      <c r="P54" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q54" s="279" t="s">
+      <c r="Q54" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R54" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="125">
         <v>54</v>
       </c>
@@ -51400,17 +51391,17 @@
       <c r="O55" s="175">
         <v>0</v>
       </c>
-      <c r="P55" s="250" t="s">
+      <c r="P55" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q55" s="279" t="s">
+      <c r="Q55" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R55" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="125">
         <v>55</v>
       </c>
@@ -51456,17 +51447,17 @@
       <c r="O56" s="175">
         <v>0</v>
       </c>
-      <c r="P56" s="250" t="s">
+      <c r="P56" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q56" s="279" t="s">
+      <c r="Q56" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R56" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="125">
         <v>56</v>
       </c>
@@ -51512,17 +51503,17 @@
       <c r="O57" s="175">
         <v>0</v>
       </c>
-      <c r="P57" s="250" t="s">
+      <c r="P57" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q57" s="279" t="s">
+      <c r="Q57" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R57" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="125">
         <v>57</v>
       </c>
@@ -51568,17 +51559,17 @@
       <c r="O58" s="175">
         <v>0</v>
       </c>
-      <c r="P58" s="250" t="s">
+      <c r="P58" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q58" s="279" t="s">
+      <c r="Q58" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R58" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="125">
         <v>58</v>
       </c>
@@ -51624,17 +51615,17 @@
       <c r="O59" s="175">
         <v>0</v>
       </c>
-      <c r="P59" s="250" t="s">
+      <c r="P59" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q59" s="279" t="s">
+      <c r="Q59" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R59" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="125">
         <v>59</v>
       </c>
@@ -51680,17 +51671,17 @@
       <c r="O60" s="175">
         <v>0</v>
       </c>
-      <c r="P60" s="250" t="s">
+      <c r="P60" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q60" s="279" t="s">
+      <c r="Q60" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R60" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="125">
         <v>60</v>
       </c>
@@ -51736,17 +51727,17 @@
       <c r="O61" s="175">
         <v>0</v>
       </c>
-      <c r="P61" s="250" t="s">
+      <c r="P61" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q61" s="279" t="s">
+      <c r="Q61" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R61" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="125">
         <v>61</v>
       </c>
@@ -51792,17 +51783,17 @@
       <c r="O62" s="175">
         <v>0</v>
       </c>
-      <c r="P62" s="250" t="s">
+      <c r="P62" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q62" s="279" t="s">
+      <c r="Q62" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R62" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="125">
         <v>62</v>
       </c>
@@ -51848,17 +51839,17 @@
       <c r="O63" s="175">
         <v>0</v>
       </c>
-      <c r="P63" s="250" t="s">
+      <c r="P63" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q63" s="279" t="s">
+      <c r="Q63" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R63" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="125">
         <v>63</v>
       </c>
@@ -51904,17 +51895,17 @@
       <c r="O64" s="175">
         <v>0</v>
       </c>
-      <c r="P64" s="250" t="s">
+      <c r="P64" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q64" s="279" t="s">
+      <c r="Q64" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R64" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="125">
         <v>64</v>
       </c>
@@ -51960,17 +51951,17 @@
       <c r="O65" s="175">
         <v>0</v>
       </c>
-      <c r="P65" s="250" t="s">
+      <c r="P65" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q65" s="279" t="s">
+      <c r="Q65" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R65" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="125">
         <v>65</v>
       </c>
@@ -52016,17 +52007,17 @@
       <c r="O66" s="175">
         <v>0</v>
       </c>
-      <c r="P66" s="250" t="s">
+      <c r="P66" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q66" s="279" t="s">
+      <c r="Q66" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R66" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="125">
         <v>66</v>
       </c>
@@ -52072,17 +52063,17 @@
       <c r="O67" s="175">
         <v>0</v>
       </c>
-      <c r="P67" s="250" t="s">
+      <c r="P67" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q67" s="279" t="s">
+      <c r="Q67" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R67" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="125">
         <v>67</v>
       </c>
@@ -52128,17 +52119,17 @@
       <c r="O68" s="175">
         <v>0</v>
       </c>
-      <c r="P68" s="250" t="s">
+      <c r="P68" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q68" s="279" t="s">
+      <c r="Q68" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R68" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="125">
         <v>68</v>
       </c>
@@ -52184,17 +52175,17 @@
       <c r="O69" s="175">
         <v>0</v>
       </c>
-      <c r="P69" s="250" t="s">
+      <c r="P69" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q69" s="279" t="s">
+      <c r="Q69" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R69" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="125">
         <v>69</v>
       </c>
@@ -52240,17 +52231,17 @@
       <c r="O70" s="175">
         <v>0</v>
       </c>
-      <c r="P70" s="250" t="s">
+      <c r="P70" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q70" s="279" t="s">
+      <c r="Q70" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R70" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="125">
         <v>70</v>
       </c>
@@ -52296,17 +52287,17 @@
       <c r="O71" s="175">
         <v>0</v>
       </c>
-      <c r="P71" s="250" t="s">
+      <c r="P71" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q71" s="279" t="s">
+      <c r="Q71" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R71" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="125">
         <v>71</v>
       </c>
@@ -52352,17 +52343,17 @@
       <c r="O72" s="175">
         <v>0</v>
       </c>
-      <c r="P72" s="250" t="s">
+      <c r="P72" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q72" s="279" t="s">
+      <c r="Q72" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R72" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="125">
         <v>72</v>
       </c>
@@ -52408,125 +52399,125 @@
       <c r="O73" s="175">
         <v>0</v>
       </c>
-      <c r="P73" s="250" t="s">
+      <c r="P73" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q73" s="279" t="s">
+      <c r="Q73" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R73" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="261">
+    <row r="74" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="258">
         <v>73</v>
       </c>
-      <c r="B74" s="262" t="s">
+      <c r="B74" s="259" t="s">
         <v>953</v>
       </c>
-      <c r="C74" s="262" t="s">
+      <c r="C74" s="259" t="s">
         <v>64</v>
       </c>
-      <c r="D74" s="262" t="s">
+      <c r="D74" s="259" t="s">
         <v>79</v>
       </c>
-      <c r="E74" s="262" t="s">
+      <c r="E74" s="259" t="s">
         <v>116</v>
       </c>
-      <c r="F74" s="263" t="s">
+      <c r="F74" s="260" t="s">
         <v>123</v>
       </c>
-      <c r="G74" s="264">
+      <c r="G74" s="261">
         <v>-8.5546120000000005</v>
       </c>
-      <c r="H74" s="265">
+      <c r="H74" s="262">
         <v>125.57374299999999</v>
       </c>
-      <c r="I74" s="266">
+      <c r="I74" s="263">
         <v>6</v>
       </c>
-      <c r="J74" s="267" t="s">
+      <c r="J74" s="264" t="s">
         <v>726</v>
       </c>
-      <c r="K74" s="263" t="s">
+      <c r="K74" s="260" t="s">
         <v>728</v>
       </c>
-      <c r="L74" s="268" t="s">
+      <c r="L74" s="265" t="s">
         <v>1371</v>
       </c>
-      <c r="M74" s="269">
-        <v>0</v>
-      </c>
-      <c r="N74" s="269">
-        <v>0</v>
-      </c>
-      <c r="O74" s="269">
-        <v>0</v>
-      </c>
-      <c r="P74" s="250" t="s">
+      <c r="M74" s="266">
+        <v>0</v>
+      </c>
+      <c r="N74" s="266">
+        <v>0</v>
+      </c>
+      <c r="O74" s="266">
+        <v>0</v>
+      </c>
+      <c r="P74" s="247" t="s">
         <v>743</v>
       </c>
-      <c r="Q74" s="279" t="s">
+      <c r="Q74" s="276" t="s">
         <v>752</v>
       </c>
       <c r="R74" s="223" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="270">
+    <row r="75" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="267">
         <v>74</v>
       </c>
-      <c r="B75" s="271" t="s">
+      <c r="B75" s="268" t="s">
         <v>1465</v>
       </c>
-      <c r="C75" s="271" t="s">
+      <c r="C75" s="268" t="s">
         <v>12</v>
       </c>
-      <c r="D75" s="271" t="s">
+      <c r="D75" s="268" t="s">
         <v>13</v>
       </c>
-      <c r="E75" s="271" t="s">
+      <c r="E75" s="268" t="s">
         <v>14</v>
       </c>
-      <c r="F75" s="272" t="s">
+      <c r="F75" s="269" t="s">
         <v>14</v>
       </c>
-      <c r="G75" s="272">
+      <c r="G75" s="269">
         <v>-8.5399999999999991</v>
       </c>
-      <c r="H75" s="273">
+      <c r="H75" s="270">
         <v>125.68</v>
       </c>
-      <c r="I75" s="274">
+      <c r="I75" s="271">
         <v>15</v>
       </c>
-      <c r="J75" s="275" t="s">
+      <c r="J75" s="272" t="s">
         <v>726</v>
       </c>
-      <c r="K75" s="272" t="s">
+      <c r="K75" s="269" t="s">
         <v>742</v>
       </c>
-      <c r="L75" s="275" t="s">
+      <c r="L75" s="272" t="s">
         <v>1432</v>
       </c>
-      <c r="M75" s="274">
-        <v>0</v>
-      </c>
-      <c r="N75" s="274">
-        <v>0</v>
-      </c>
-      <c r="O75" s="274">
+      <c r="M75" s="271">
+        <v>0</v>
+      </c>
+      <c r="N75" s="271">
+        <v>0</v>
+      </c>
+      <c r="O75" s="271">
         <v>4</v>
       </c>
-      <c r="P75" s="276" t="s">
+      <c r="P75" s="273" t="s">
         <v>744</v>
       </c>
-      <c r="Q75" s="280" t="s">
+      <c r="Q75" s="277" t="s">
         <v>752</v>
       </c>
-      <c r="R75" s="275" t="s">
+      <c r="R75" s="272" t="s">
         <v>576</v>
       </c>
     </row>
@@ -52542,29 +52533,29 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:R50"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.19921875" style="16" customWidth="1"/>
-    <col min="2" max="2" width="44.09765625" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44" style="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.796875" style="17" customWidth="1"/>
     <col min="4" max="4" width="24.19921875" style="17" customWidth="1"/>
     <col min="5" max="6" width="21.59765625" style="17" customWidth="1"/>
-    <col min="7" max="7" width="13.296875" style="25" customWidth="1"/>
+    <col min="7" max="7" width="13.19921875" style="25" customWidth="1"/>
     <col min="8" max="8" width="14.3984375" style="13" customWidth="1"/>
     <col min="9" max="9" width="16" style="9" customWidth="1"/>
     <col min="10" max="10" width="13.59765625" style="8" customWidth="1"/>
     <col min="11" max="11" width="28.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.3984375" style="8" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.3984375" style="9" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.796875" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.59765625" style="9" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="55" style="8" customWidth="1"/>
     <col min="17" max="17" width="38.3984375" style="8" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="39.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="19" max="16384" width="8.796875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="16" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="16" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="22" t="s">
         <v>520</v>
       </c>
@@ -52620,11 +52611,11 @@
         <v>717</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="79">
         <v>1</v>
       </c>
-      <c r="B2" s="251" t="s">
+      <c r="B2" s="248" t="s">
         <v>1489</v>
       </c>
       <c r="C2" s="147" t="s">
@@ -52676,7 +52667,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="34">
         <v>2</v>
       </c>
@@ -52722,7 +52713,7 @@
       <c r="O3" s="149">
         <v>7</v>
       </c>
-      <c r="P3" s="252" t="s">
+      <c r="P3" s="249" t="s">
         <v>1427</v>
       </c>
       <c r="Q3" s="217" t="s">
@@ -52732,7 +52723,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="34">
         <v>3</v>
       </c>
@@ -52778,7 +52769,7 @@
       <c r="O4" s="38">
         <v>5</v>
       </c>
-      <c r="P4" s="252" t="s">
+      <c r="P4" s="249" t="s">
         <v>1427</v>
       </c>
       <c r="Q4" s="217" t="s">
@@ -52788,7 +52779,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="34">
         <v>4</v>
       </c>
@@ -52834,7 +52825,7 @@
       <c r="O5" s="38">
         <v>4</v>
       </c>
-      <c r="P5" s="252" t="s">
+      <c r="P5" s="249" t="s">
         <v>1427</v>
       </c>
       <c r="Q5" s="217" t="s">
@@ -52844,7 +52835,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="34">
         <v>5</v>
       </c>
@@ -52890,7 +52881,7 @@
       <c r="O6" s="38">
         <v>10</v>
       </c>
-      <c r="P6" s="252" t="s">
+      <c r="P6" s="249" t="s">
         <v>1427</v>
       </c>
       <c r="Q6" s="217" t="s">
@@ -52900,7 +52891,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="34">
         <v>6</v>
       </c>
@@ -52946,7 +52937,7 @@
       <c r="O7" s="38">
         <v>6</v>
       </c>
-      <c r="P7" s="252" t="s">
+      <c r="P7" s="249" t="s">
         <v>1427</v>
       </c>
       <c r="Q7" s="217" t="s">
@@ -52956,7 +52947,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="34">
         <v>7</v>
       </c>
@@ -53002,7 +52993,7 @@
       <c r="O8" s="38">
         <v>2</v>
       </c>
-      <c r="P8" s="252" t="s">
+      <c r="P8" s="249" t="s">
         <v>1427</v>
       </c>
       <c r="Q8" s="217" t="s">
@@ -53012,7 +53003,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="40">
         <v>8</v>
       </c>
@@ -53061,14 +53052,14 @@
       <c r="P9" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q9" s="243" t="s">
+      <c r="Q9" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R9" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="40">
         <v>9</v>
       </c>
@@ -53117,14 +53108,14 @@
       <c r="P10" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q10" s="243" t="s">
+      <c r="Q10" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R10" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="40">
         <v>10</v>
       </c>
@@ -53173,14 +53164,14 @@
       <c r="P11" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q11" s="243" t="s">
+      <c r="Q11" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R11" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="40">
         <v>11</v>
       </c>
@@ -53229,14 +53220,14 @@
       <c r="P12" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q12" s="243" t="s">
+      <c r="Q12" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R12" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="40">
         <v>12</v>
       </c>
@@ -53285,14 +53276,14 @@
       <c r="P13" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q13" s="243" t="s">
+      <c r="Q13" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R13" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="40">
         <v>13</v>
       </c>
@@ -53341,14 +53332,14 @@
       <c r="P14" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q14" s="243" t="s">
+      <c r="Q14" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R14" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="40">
         <v>14</v>
       </c>
@@ -53397,14 +53388,14 @@
       <c r="P15" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q15" s="243" t="s">
+      <c r="Q15" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R15" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="40">
         <v>15</v>
       </c>
@@ -53453,14 +53444,14 @@
       <c r="P16" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q16" s="243" t="s">
+      <c r="Q16" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R16" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="40">
         <v>16</v>
       </c>
@@ -53509,14 +53500,14 @@
       <c r="P17" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q17" s="243" t="s">
+      <c r="Q17" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R17" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="40">
         <v>17</v>
       </c>
@@ -53565,14 +53556,14 @@
       <c r="P18" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q18" s="243" t="s">
+      <c r="Q18" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R18" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="40">
         <v>18</v>
       </c>
@@ -53621,14 +53612,14 @@
       <c r="P19" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q19" s="243" t="s">
+      <c r="Q19" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R19" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="40">
         <v>19</v>
       </c>
@@ -53677,14 +53668,14 @@
       <c r="P20" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q20" s="243" t="s">
+      <c r="Q20" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R20" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="40">
         <v>20</v>
       </c>
@@ -53733,14 +53724,14 @@
       <c r="P21" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q21" s="243" t="s">
+      <c r="Q21" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R21" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="40">
         <v>21</v>
       </c>
@@ -53789,14 +53780,14 @@
       <c r="P22" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q22" s="243" t="s">
+      <c r="Q22" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R22" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="40">
         <v>22</v>
       </c>
@@ -53845,14 +53836,14 @@
       <c r="P23" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q23" s="243" t="s">
+      <c r="Q23" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R23" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="40">
         <v>23</v>
       </c>
@@ -53901,14 +53892,14 @@
       <c r="P24" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q24" s="243" t="s">
+      <c r="Q24" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R24" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="40">
         <v>24</v>
       </c>
@@ -53957,14 +53948,14 @@
       <c r="P25" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q25" s="243" t="s">
+      <c r="Q25" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R25" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="40">
         <v>25</v>
       </c>
@@ -54013,14 +54004,14 @@
       <c r="P26" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q26" s="243" t="s">
+      <c r="Q26" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R26" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="40">
         <v>26</v>
       </c>
@@ -54069,14 +54060,14 @@
       <c r="P27" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q27" s="243" t="s">
+      <c r="Q27" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R27" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="40">
         <v>27</v>
       </c>
@@ -54125,14 +54116,14 @@
       <c r="P28" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q28" s="243" t="s">
+      <c r="Q28" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R28" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="40">
         <v>28</v>
       </c>
@@ -54181,14 +54172,14 @@
       <c r="P29" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q29" s="243" t="s">
+      <c r="Q29" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R29" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="40">
         <v>29</v>
       </c>
@@ -54237,14 +54228,14 @@
       <c r="P30" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q30" s="243" t="s">
+      <c r="Q30" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R30" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="40">
         <v>30</v>
       </c>
@@ -54293,14 +54284,14 @@
       <c r="P31" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q31" s="243" t="s">
+      <c r="Q31" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R31" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="40">
         <v>31</v>
       </c>
@@ -54349,14 +54340,14 @@
       <c r="P32" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q32" s="243" t="s">
+      <c r="Q32" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R32" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="40">
         <v>32</v>
       </c>
@@ -54405,14 +54396,14 @@
       <c r="P33" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q33" s="243" t="s">
+      <c r="Q33" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R33" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="40">
         <v>33</v>
       </c>
@@ -54461,14 +54452,14 @@
       <c r="P34" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q34" s="243" t="s">
+      <c r="Q34" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R34" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="40">
         <v>34</v>
       </c>
@@ -54517,14 +54508,14 @@
       <c r="P35" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q35" s="243" t="s">
+      <c r="Q35" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R35" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="40">
         <v>35</v>
       </c>
@@ -54573,14 +54564,14 @@
       <c r="P36" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q36" s="243" t="s">
+      <c r="Q36" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R36" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="40">
         <v>36</v>
       </c>
@@ -54629,14 +54620,14 @@
       <c r="P37" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q37" s="243" t="s">
+      <c r="Q37" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R37" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="40">
         <v>37</v>
       </c>
@@ -54685,14 +54676,14 @@
       <c r="P38" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q38" s="243" t="s">
+      <c r="Q38" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R38" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="40">
         <v>38</v>
       </c>
@@ -54741,14 +54732,14 @@
       <c r="P39" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q39" s="243" t="s">
+      <c r="Q39" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R39" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="40">
         <v>39</v>
       </c>
@@ -54797,14 +54788,14 @@
       <c r="P40" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q40" s="243" t="s">
+      <c r="Q40" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R40" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="40">
         <v>40</v>
       </c>
@@ -54853,14 +54844,14 @@
       <c r="P41" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q41" s="243" t="s">
+      <c r="Q41" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R41" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="40">
         <v>41</v>
       </c>
@@ -54909,14 +54900,14 @@
       <c r="P42" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q42" s="243" t="s">
+      <c r="Q42" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R42" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="40">
         <v>42</v>
       </c>
@@ -54965,14 +54956,14 @@
       <c r="P43" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q43" s="243" t="s">
+      <c r="Q43" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R43" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="40">
         <v>43</v>
       </c>
@@ -55021,14 +55012,14 @@
       <c r="P44" s="221" t="s">
         <v>1428</v>
       </c>
-      <c r="Q44" s="243" t="s">
+      <c r="Q44" s="240" t="s">
         <v>746</v>
       </c>
       <c r="R44" s="220" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="52">
         <v>44</v>
       </c>
@@ -55074,17 +55065,17 @@
       <c r="O45" s="145">
         <v>1</v>
       </c>
-      <c r="P45" s="245" t="s">
+      <c r="P45" s="242" t="s">
         <v>1429</v>
       </c>
-      <c r="Q45" s="246" t="s">
+      <c r="Q45" s="243" t="s">
         <v>718</v>
       </c>
-      <c r="R45" s="246" t="s">
+      <c r="R45" s="243" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="52">
         <v>45</v>
       </c>
@@ -55130,17 +55121,17 @@
       <c r="O46" s="145">
         <v>1</v>
       </c>
-      <c r="P46" s="245" t="s">
+      <c r="P46" s="242" t="s">
         <v>1429</v>
       </c>
-      <c r="Q46" s="246" t="s">
+      <c r="Q46" s="243" t="s">
         <v>718</v>
       </c>
-      <c r="R46" s="246" t="s">
+      <c r="R46" s="243" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="52">
         <v>46</v>
       </c>
@@ -55186,17 +55177,17 @@
       <c r="O47" s="145">
         <v>4</v>
       </c>
-      <c r="P47" s="245" t="s">
+      <c r="P47" s="242" t="s">
         <v>1429</v>
       </c>
-      <c r="Q47" s="246" t="s">
+      <c r="Q47" s="243" t="s">
         <v>718</v>
       </c>
-      <c r="R47" s="246" t="s">
+      <c r="R47" s="243" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="52">
         <v>47</v>
       </c>
@@ -55242,17 +55233,17 @@
       <c r="O48" s="145">
         <v>5</v>
       </c>
-      <c r="P48" s="245" t="s">
+      <c r="P48" s="242" t="s">
         <v>1429</v>
       </c>
-      <c r="Q48" s="246" t="s">
+      <c r="Q48" s="243" t="s">
         <v>718</v>
       </c>
-      <c r="R48" s="246" t="s">
+      <c r="R48" s="243" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="52">
         <v>48</v>
       </c>
@@ -55298,17 +55289,17 @@
       <c r="O49" s="145">
         <v>4</v>
       </c>
-      <c r="P49" s="245" t="s">
+      <c r="P49" s="242" t="s">
         <v>1429</v>
       </c>
-      <c r="Q49" s="246" t="s">
+      <c r="Q49" s="243" t="s">
         <v>718</v>
       </c>
-      <c r="R49" s="246" t="s">
+      <c r="R49" s="243" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" ht="20.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="52">
         <v>49</v>
       </c>
